--- a/results/542_z06/5_quantification/542_z06_quantification.xlsx
+++ b/results/542_z06/5_quantification/542_z06_quantification.xlsx
@@ -460,13 +460,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D2" t="n">
         <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4">
@@ -539,7 +539,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7">
@@ -568,7 +568,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8">
@@ -597,7 +597,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9">
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10">
@@ -655,7 +655,7 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11">
@@ -684,7 +684,7 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12">
@@ -699,13 +699,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>10.9231</v>
+        <v>11</v>
       </c>
       <c r="D12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E12" t="n">
-        <v>4.4993</v>
+        <v>5.8045</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13">
@@ -728,13 +728,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>422.0769</v>
+        <v>433.1429</v>
       </c>
       <c r="D13" t="n">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="E13" t="n">
-        <v>169.9826</v>
+        <v>196.8294</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14">
@@ -757,13 +757,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1022.4615</v>
+        <v>995.9286</v>
       </c>
       <c r="D14" t="n">
-        <v>975</v>
+        <v>923.5</v>
       </c>
       <c r="E14" t="n">
-        <v>363.3448</v>
+        <v>437.7301</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
@@ -786,13 +786,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2108.3707</v>
+        <v>2104.0271</v>
       </c>
       <c r="D15" t="n">
-        <v>1773.1829</v>
+        <v>1924.3028</v>
       </c>
       <c r="E15" t="n">
-        <v>1287.2304</v>
+        <v>1562.1019</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16">
@@ -815,13 +815,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>88.1538</v>
+        <v>92.28570000000001</v>
       </c>
       <c r="D16" t="n">
-        <v>79</v>
+        <v>78.5</v>
       </c>
       <c r="E16" t="n">
-        <v>56.4341</v>
+        <v>70.267</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17">
@@ -844,13 +844,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>24.5932</v>
+        <v>22.7907</v>
       </c>
       <c r="D17" t="n">
-        <v>24.3648</v>
+        <v>22.6947</v>
       </c>
       <c r="E17" t="n">
-        <v>3.2562</v>
+        <v>4.1278</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="18">
@@ -873,13 +873,13 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>297.8123</v>
+        <v>280.6021</v>
       </c>
       <c r="D18" t="n">
-        <v>309.5219</v>
+        <v>305.9864</v>
       </c>
       <c r="E18" t="n">
-        <v>115.1171</v>
+        <v>127.9813</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19">
@@ -902,13 +902,13 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>10771.6923</v>
+        <v>10209.4286</v>
       </c>
       <c r="D19" t="n">
-        <v>11337</v>
+        <v>11138.5</v>
       </c>
       <c r="E19" t="n">
-        <v>2967.4305</v>
+        <v>3432.1456</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="20">
@@ -931,13 +931,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>25565.4615</v>
+        <v>23888.4286</v>
       </c>
       <c r="D20" t="n">
-        <v>27170</v>
+        <v>25904.5</v>
       </c>
       <c r="E20" t="n">
-        <v>6351.0485</v>
+        <v>7904.5602</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21">
@@ -974,7 +974,7 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="22">
@@ -989,13 +989,13 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.9908</v>
+        <v>0.9913999999999999</v>
       </c>
       <c r="D22" t="n">
         <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0272</v>
+        <v>0.0263</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.03830376</v>
+        <v>0.04140095</v>
       </c>
       <c r="D23" t="n">
-        <v>0.03836994</v>
+        <v>0.04064855</v>
       </c>
       <c r="E23" t="n">
-        <v>0.00697074</v>
+        <v>0.00716751</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="24">
@@ -1047,13 +1047,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.03934038</v>
+        <v>0.04048473</v>
       </c>
       <c r="D24" t="n">
-        <v>0.03891867</v>
+        <v>0.03924596</v>
       </c>
       <c r="E24" t="n">
-        <v>0.00589092</v>
+        <v>0.00640785</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="25">
@@ -1076,13 +1076,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>3.7216</v>
+        <v>4.0757</v>
       </c>
       <c r="D25" t="n">
-        <v>3.7827</v>
+        <v>4.0826</v>
       </c>
       <c r="E25" t="n">
-        <v>0.7614</v>
+        <v>1.2805</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="26">
@@ -1105,13 +1105,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>356.4615</v>
+        <v>379.2857</v>
       </c>
       <c r="D26" t="n">
-        <v>313</v>
+        <v>335</v>
       </c>
       <c r="E26" t="n">
-        <v>172.8268</v>
+        <v>202.6245</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="27">
@@ -1134,13 +1134,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>745.8462</v>
+        <v>789</v>
       </c>
       <c r="D27" t="n">
-        <v>668</v>
+        <v>619</v>
       </c>
       <c r="E27" t="n">
-        <v>398.9607</v>
+        <v>478.9541</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="28">
@@ -1163,13 +1163,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>478.7993</v>
+        <v>492.1853</v>
       </c>
       <c r="D28" t="n">
-        <v>441.1615</v>
+        <v>450.9544</v>
       </c>
       <c r="E28" t="n">
-        <v>195.4962</v>
+        <v>225.1756</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="29">
@@ -1192,13 +1192,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1157.4735</v>
+        <v>1128.49</v>
       </c>
       <c r="D29" t="n">
-        <v>1100.9626</v>
+        <v>1034.4651</v>
       </c>
       <c r="E29" t="n">
-        <v>416.8483</v>
+        <v>500.3153</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="30">
@@ -1221,13 +1221,13 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>9.461499999999999</v>
+        <v>9.357100000000001</v>
       </c>
       <c r="D30" t="n">
         <v>9</v>
       </c>
       <c r="E30" t="n">
-        <v>4.1955</v>
+        <v>5.078</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="31">
@@ -1250,13 +1250,13 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>13.4615</v>
+        <v>13.1429</v>
       </c>
       <c r="D31" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E31" t="n">
-        <v>5.2697</v>
+        <v>5.4187</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="32">
@@ -1279,13 +1279,13 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>14.0769</v>
+        <v>13.2143</v>
       </c>
       <c r="D32" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="n">
-        <v>5.5597</v>
+        <v>5.7536</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="33">
@@ -1308,13 +1308,13 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>6.6809</v>
+        <v>7.4897</v>
       </c>
       <c r="D33" t="n">
-        <v>6.6928</v>
+        <v>7.4857</v>
       </c>
       <c r="E33" t="n">
-        <v>0.4577</v>
+        <v>0.4228</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -1336,7 +1336,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1373,7 +1373,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1009061</v>
+        <v>1008847</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>37752</v>
+        <v>39263</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.037413</v>
+        <v>0.03891869</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>748</v>
+        <v>863</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.00074128</v>
+        <v>0.00085543</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1.586e-05</v>
+        <v>1.685e-05</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>284</v>
+        <v>248</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>132.9296</v>
+        <v>158.3185</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>27.5</v>
+        <v>25</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.04234794</v>
+        <v>0.04408455</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.03737811</v>
+        <v>0.03886559</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1613,6 +1613,86 @@
         </is>
       </c>
       <c r="D14" t="inlineStr">
+        <is>
+          <t>px^-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>unattached_length_px</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>362</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>px</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>unattached_component_count</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>19</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>canalicular_length_density_attached_per_px</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>0.03891869</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>px^-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>field_length_density_with_unattached_per_px</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>0.03927751</v>
+      </c>
+      <c r="D18" t="inlineStr">
         <is>
           <t>px^-1</t>
         </is>
@@ -1666,7 +1746,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7.3668</v>
+        <v>8.154500000000001</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1686,7 +1766,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>8.2462</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1706,7 +1786,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>5.6569</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1726,7 +1806,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>10</v>
+        <v>10.7703</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1746,7 +1826,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>36570</v>
+        <v>38017</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1904,7 +1984,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>15.2858</v>
+        <v>15.5058</v>
       </c>
     </row>
     <row r="10">
@@ -1919,7 +1999,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.3677</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="11">
@@ -1934,7 +2014,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>36.3873</v>
+        <v>36.7054</v>
       </c>
     </row>
     <row r="12">
@@ -1949,7 +2029,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>50.034</v>
+        <v>50.0471</v>
       </c>
     </row>
     <row r="13">
@@ -1964,7 +2044,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.2507</v>
+        <v>0.2493</v>
       </c>
     </row>
     <row r="14">
@@ -1979,7 +2059,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.7493</v>
+        <v>0.7507</v>
       </c>
     </row>
     <row r="15">
@@ -2026,7 +2106,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="18">
@@ -2041,7 +2121,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19">
@@ -2056,7 +2136,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -2071,7 +2151,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -2135,7 +2215,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1.04</v>
+        <v>1.072</v>
       </c>
     </row>
     <row r="25">
@@ -2150,7 +2230,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.52</v>
+        <v>0.7354000000000001</v>
       </c>
     </row>
     <row r="26">
@@ -2165,7 +2245,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1.3</v>
+        <v>1.4001</v>
       </c>
     </row>
   </sheetData>
@@ -2179,7 +2259,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG17"/>
+  <dimension ref="A1:AG18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2384,22 +2464,22 @@
         <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M2" t="n">
-        <v>203</v>
+        <v>218</v>
       </c>
       <c r="N2" t="n">
-        <v>553</v>
+        <v>581</v>
       </c>
       <c r="O2" t="n">
-        <v>677.2864</v>
+        <v>894.4113</v>
       </c>
       <c r="P2" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="Q2" t="n">
-        <v>30.7857</v>
+        <v>28.852</v>
       </c>
       <c r="R2" t="n">
         <v>215.2315</v>
@@ -2417,25 +2497,25 @@
         <v>0.5983000000000001</v>
       </c>
       <c r="W2" t="n">
-        <v>0.03614029</v>
+        <v>0.03881075</v>
       </c>
       <c r="X2" t="n">
-        <v>0.04356389</v>
+        <v>0.04576965</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.3231</v>
+        <v>2.7877</v>
       </c>
       <c r="Z2" t="n">
-        <v>203</v>
+        <v>218</v>
       </c>
       <c r="AA2" t="n">
-        <v>495</v>
+        <v>574</v>
       </c>
       <c r="AB2" t="n">
-        <v>231.4092</v>
+        <v>251.066</v>
       </c>
       <c r="AC2" t="n">
-        <v>633.7716</v>
+        <v>663.7006</v>
       </c>
       <c r="AD2" t="n">
         <v>6</v>
@@ -2447,7 +2527,7 @@
         <v>5</v>
       </c>
       <c r="AG2" t="n">
-        <v>6.9395</v>
+        <v>7.8557</v>
       </c>
     </row>
     <row r="3">
@@ -2485,22 +2565,22 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M3" t="n">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="N3" t="n">
-        <v>492</v>
+        <v>502</v>
       </c>
       <c r="O3" t="n">
-        <v>781.7422</v>
+        <v>825.0265000000001</v>
       </c>
       <c r="P3" t="n">
         <v>30</v>
       </c>
       <c r="Q3" t="n">
-        <v>26.0581</v>
+        <v>27.5009</v>
       </c>
       <c r="R3" t="n">
         <v>126.468</v>
@@ -2518,37 +2598,37 @@
         <v>1</v>
       </c>
       <c r="W3" t="n">
-        <v>0.03003534</v>
+        <v>0.03115965</v>
       </c>
       <c r="X3" t="n">
-        <v>0.03325673</v>
+        <v>0.03393268</v>
       </c>
       <c r="Y3" t="n">
-        <v>3.1629</v>
+        <v>4.7443</v>
       </c>
       <c r="Z3" t="n">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="AA3" t="n">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="AB3" t="n">
-        <v>217.1371</v>
+        <v>224.1371</v>
       </c>
       <c r="AC3" t="n">
-        <v>553.4457</v>
+        <v>565.5168</v>
       </c>
       <c r="AD3" t="n">
         <v>4</v>
       </c>
       <c r="AE3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF3" t="n">
         <v>10</v>
       </c>
       <c r="AG3" t="n">
-        <v>7.3126</v>
+        <v>7.7664</v>
       </c>
     </row>
     <row r="4">
@@ -2586,22 +2666,22 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M4" t="n">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="N4" t="n">
-        <v>696</v>
+        <v>689</v>
       </c>
       <c r="O4" t="n">
-        <v>1008.6194</v>
+        <v>1352.2834</v>
       </c>
       <c r="P4" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="Q4" t="n">
-        <v>24.6005</v>
+        <v>29.3975</v>
       </c>
       <c r="R4" t="n">
         <v>160.6396</v>
@@ -2619,37 +2699,37 @@
         <v>0.9774</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0412844</v>
+        <v>0.04028096</v>
       </c>
       <c r="X4" t="n">
-        <v>0.03702325</v>
+        <v>0.03665089</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.9801</v>
+        <v>4.3576</v>
       </c>
       <c r="Z4" t="n">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="AA4" t="n">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="AB4" t="n">
-        <v>334.463</v>
+        <v>327.8772</v>
       </c>
       <c r="AC4" t="n">
-        <v>793.4823</v>
+        <v>786.8964999999999</v>
       </c>
       <c r="AD4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AE4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AF4" t="n">
         <v>5</v>
       </c>
       <c r="AG4" t="n">
-        <v>6.256</v>
+        <v>7.1332</v>
       </c>
     </row>
     <row r="5">
@@ -2687,22 +2767,22 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M5" t="n">
-        <v>231</v>
+        <v>255</v>
       </c>
       <c r="N5" t="n">
-        <v>634</v>
+        <v>657</v>
       </c>
       <c r="O5" t="n">
-        <v>457.6468</v>
+        <v>344.5219</v>
       </c>
       <c r="P5" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="Q5" t="n">
-        <v>26.9204</v>
+        <v>18.1327</v>
       </c>
       <c r="R5" t="n">
         <v>151.7817</v>
@@ -2720,25 +2800,25 @@
         <v>1</v>
       </c>
       <c r="W5" t="n">
-        <v>0.03421209</v>
+        <v>0.03776659</v>
       </c>
       <c r="X5" t="n">
-        <v>0.04138111</v>
+        <v>0.04288232</v>
       </c>
       <c r="Y5" t="n">
-        <v>4.6119</v>
+        <v>3.953</v>
       </c>
       <c r="Z5" t="n">
-        <v>179</v>
+        <v>211</v>
       </c>
       <c r="AA5" t="n">
-        <v>243</v>
+        <v>338</v>
       </c>
       <c r="AB5" t="n">
-        <v>259.7229</v>
+        <v>285.9655</v>
       </c>
       <c r="AC5" t="n">
-        <v>713.9138</v>
+        <v>736.2569</v>
       </c>
       <c r="AD5" t="n">
         <v>5</v>
@@ -2750,7 +2830,7 @@
         <v>8</v>
       </c>
       <c r="AG5" t="n">
-        <v>6.4503</v>
+        <v>7.3342</v>
       </c>
     </row>
     <row r="6">
@@ -2788,22 +2868,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M6" t="n">
-        <v>334</v>
+        <v>380</v>
       </c>
       <c r="N6" t="n">
-        <v>975</v>
+        <v>1031</v>
       </c>
       <c r="O6" t="n">
-        <v>2532.6896</v>
+        <v>2055.5992</v>
       </c>
       <c r="P6" t="n">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="Q6" t="n">
-        <v>23.8933</v>
+        <v>24.4714</v>
       </c>
       <c r="R6" t="n">
         <v>322.0427</v>
@@ -2821,37 +2901,37 @@
         <v>1</v>
       </c>
       <c r="W6" t="n">
-        <v>0.02863757</v>
+        <v>0.03258167</v>
       </c>
       <c r="X6" t="n">
-        <v>0.03398989</v>
+        <v>0.03594213</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.7947</v>
+        <v>2.1736</v>
       </c>
       <c r="Z6" t="n">
-        <v>275</v>
+        <v>319</v>
       </c>
       <c r="AA6" t="n">
-        <v>682</v>
+        <v>837</v>
       </c>
       <c r="AB6" t="n">
-        <v>378.1198</v>
+        <v>437.6468</v>
       </c>
       <c r="AC6" t="n">
-        <v>1100.9626</v>
+        <v>1179.5311</v>
       </c>
       <c r="AD6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE6" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AF6" t="n">
         <v>13</v>
       </c>
       <c r="AG6" t="n">
-        <v>6.531</v>
+        <v>7.2803</v>
       </c>
     </row>
     <row r="7">
@@ -2889,22 +2969,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="M7" t="n">
-        <v>743</v>
+        <v>784</v>
       </c>
       <c r="N7" t="n">
-        <v>1607</v>
+        <v>1661</v>
       </c>
       <c r="O7" t="n">
-        <v>4800.703</v>
+        <v>5837.1021</v>
       </c>
       <c r="P7" t="n">
-        <v>199</v>
+        <v>238</v>
       </c>
       <c r="Q7" t="n">
-        <v>24.1241</v>
+        <v>24.5256</v>
       </c>
       <c r="R7" t="n">
         <v>438.5168</v>
@@ -2922,37 +3002,37 @@
         <v>1</v>
       </c>
       <c r="W7" t="n">
-        <v>0.05344939</v>
+        <v>0.05639882</v>
       </c>
       <c r="X7" t="n">
-        <v>0.05082869</v>
+        <v>0.05253669</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.1047</v>
+        <v>5.0169</v>
       </c>
       <c r="Z7" t="n">
-        <v>713</v>
+        <v>781</v>
       </c>
       <c r="AA7" t="n">
-        <v>1487</v>
+        <v>1566</v>
       </c>
       <c r="AB7" t="n">
-        <v>862.0509</v>
+        <v>902.4651</v>
       </c>
       <c r="AC7" t="n">
-        <v>1863.185</v>
+        <v>1908.8297</v>
       </c>
       <c r="AD7" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AE7" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AF7" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AG7" t="n">
-        <v>6.704</v>
+        <v>7.6259</v>
       </c>
     </row>
     <row r="8">
@@ -2990,31 +3070,31 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="M8" t="n">
-        <v>383</v>
+        <v>410</v>
       </c>
       <c r="N8" t="n">
-        <v>835</v>
+        <v>749</v>
       </c>
       <c r="O8" t="n">
-        <v>983.8671000000001</v>
+        <v>822.1981</v>
       </c>
       <c r="P8" t="n">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="Q8" t="n">
-        <v>19.2915</v>
+        <v>22.8388</v>
       </c>
       <c r="R8" t="n">
         <v>211.9239</v>
       </c>
       <c r="S8" t="n">
-        <v>8845</v>
+        <v>8423</v>
       </c>
       <c r="T8" t="n">
-        <v>21455</v>
+        <v>18846</v>
       </c>
       <c r="U8" t="n">
         <v>1</v>
@@ -3023,25 +3103,25 @@
         <v>1</v>
       </c>
       <c r="W8" t="n">
-        <v>0.0433013</v>
+        <v>0.04867624</v>
       </c>
       <c r="X8" t="n">
-        <v>0.03891867</v>
+        <v>0.03974318</v>
       </c>
       <c r="Y8" t="n">
-        <v>4.2468</v>
+        <v>6.6061</v>
       </c>
       <c r="Z8" t="n">
-        <v>312</v>
+        <v>351</v>
       </c>
       <c r="AA8" t="n">
-        <v>664</v>
+        <v>547</v>
       </c>
       <c r="AB8" t="n">
-        <v>427.7056</v>
+        <v>464.262</v>
       </c>
       <c r="AC8" t="n">
-        <v>941.3524</v>
+        <v>849.5118</v>
       </c>
       <c r="AD8" t="n">
         <v>8</v>
@@ -3050,10 +3130,10 @@
         <v>12</v>
       </c>
       <c r="AF8" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AG8" t="n">
-        <v>6.6928</v>
+        <v>7.4551</v>
       </c>
     </row>
     <row r="9">
@@ -3091,22 +3171,22 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="M9" t="n">
-        <v>431</v>
+        <v>459</v>
       </c>
       <c r="N9" t="n">
-        <v>863</v>
+        <v>887</v>
       </c>
       <c r="O9" t="n">
-        <v>1726.1362</v>
+        <v>1793.0063</v>
       </c>
       <c r="P9" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="Q9" t="n">
-        <v>21.8498</v>
+        <v>21.6025</v>
       </c>
       <c r="R9" t="n">
         <v>359.1909</v>
@@ -3124,37 +3204,37 @@
         <v>0.9025</v>
       </c>
       <c r="W9" t="n">
-        <v>0.03480578</v>
+        <v>0.03706695</v>
       </c>
       <c r="X9" t="n">
-        <v>0.03192276</v>
+        <v>0.03281053</v>
       </c>
       <c r="Y9" t="n">
-        <v>4.4545</v>
+        <v>3.8976</v>
       </c>
       <c r="Z9" t="n">
-        <v>385</v>
+        <v>415</v>
       </c>
       <c r="AA9" t="n">
-        <v>668</v>
+        <v>691</v>
       </c>
       <c r="AB9" t="n">
-        <v>478.0904</v>
+        <v>514.3036</v>
       </c>
       <c r="AC9" t="n">
-        <v>964.7666</v>
+        <v>993.6661</v>
       </c>
       <c r="AD9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AE9" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AF9" t="n">
         <v>10</v>
       </c>
       <c r="AG9" t="n">
-        <v>6.7312</v>
+        <v>7.5163</v>
       </c>
     </row>
     <row r="10">
@@ -3192,31 +3272,31 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M10" t="n">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="N10" t="n">
-        <v>1003</v>
+        <v>960</v>
       </c>
       <c r="O10" t="n">
-        <v>3049.378</v>
+        <v>2255.055</v>
       </c>
       <c r="P10" t="n">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="Q10" t="n">
-        <v>25.8422</v>
+        <v>22.5506</v>
       </c>
       <c r="R10" t="n">
         <v>302.4508</v>
       </c>
       <c r="S10" t="n">
-        <v>11295</v>
+        <v>10940</v>
       </c>
       <c r="T10" t="n">
-        <v>27170</v>
+        <v>24775</v>
       </c>
       <c r="U10" t="n">
         <v>1</v>
@@ -3225,25 +3305,25 @@
         <v>1</v>
       </c>
       <c r="W10" t="n">
-        <v>0.03461709</v>
+        <v>0.03546618</v>
       </c>
       <c r="X10" t="n">
-        <v>0.03691572</v>
+        <v>0.03874874</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.3144</v>
+        <v>1.9838</v>
       </c>
       <c r="Z10" t="n">
-        <v>313</v>
+        <v>301</v>
       </c>
       <c r="AA10" t="n">
-        <v>555</v>
+        <v>537</v>
       </c>
       <c r="AB10" t="n">
-        <v>441.1615</v>
+        <v>436.0904</v>
       </c>
       <c r="AC10" t="n">
-        <v>1124.7199</v>
+        <v>1075.2641</v>
       </c>
       <c r="AD10" t="n">
         <v>11</v>
@@ -3252,10 +3332,10 @@
         <v>14</v>
       </c>
       <c r="AF10" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AG10" t="n">
-        <v>7.7634</v>
+        <v>8.5387</v>
       </c>
     </row>
     <row r="11">
@@ -3293,22 +3373,22 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="M11" t="n">
-        <v>435</v>
+        <v>465</v>
       </c>
       <c r="N11" t="n">
-        <v>1212</v>
+        <v>1270</v>
       </c>
       <c r="O11" t="n">
-        <v>2345.3221</v>
+        <v>3369.3191</v>
       </c>
       <c r="P11" t="n">
-        <v>90</v>
+        <v>138</v>
       </c>
       <c r="Q11" t="n">
-        <v>26.0591</v>
+        <v>24.4154</v>
       </c>
       <c r="R11" t="n">
         <v>309.5219</v>
@@ -3326,25 +3406,25 @@
         <v>1</v>
       </c>
       <c r="W11" t="n">
-        <v>0.03836994</v>
+        <v>0.04101614</v>
       </c>
       <c r="X11" t="n">
-        <v>0.04284805</v>
+        <v>0.04489854</v>
       </c>
       <c r="Y11" t="n">
-        <v>3.8769</v>
+        <v>5.1693</v>
       </c>
       <c r="Z11" t="n">
-        <v>413</v>
+        <v>444</v>
       </c>
       <c r="AA11" t="n">
-        <v>973</v>
+        <v>1094</v>
       </c>
       <c r="AB11" t="n">
-        <v>499.2742</v>
+        <v>534.5168</v>
       </c>
       <c r="AC11" t="n">
-        <v>1389.6976</v>
+        <v>1452.8692</v>
       </c>
       <c r="AD11" t="n">
         <v>10</v>
@@ -3356,7 +3436,7 @@
         <v>15</v>
       </c>
       <c r="AG11" t="n">
-        <v>6.864</v>
+        <v>7.7735</v>
       </c>
     </row>
     <row r="12">
@@ -3394,22 +3474,22 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="M12" t="n">
-        <v>678</v>
+        <v>767</v>
       </c>
       <c r="N12" t="n">
-        <v>1693</v>
+        <v>1786</v>
       </c>
       <c r="O12" t="n">
-        <v>3915.5222</v>
+        <v>4279.8309</v>
       </c>
       <c r="P12" t="n">
-        <v>186</v>
+        <v>224</v>
       </c>
       <c r="Q12" t="n">
-        <v>21.0512</v>
+        <v>19.1064</v>
       </c>
       <c r="R12" t="n">
         <v>468.2742</v>
@@ -3427,37 +3507,37 @@
         <v>1</v>
       </c>
       <c r="W12" t="n">
-        <v>0.04413201</v>
+        <v>0.04992514</v>
       </c>
       <c r="X12" t="n">
-        <v>0.04965392</v>
+        <v>0.05238151</v>
       </c>
       <c r="Y12" t="n">
-        <v>3.4168</v>
+        <v>3.8439</v>
       </c>
       <c r="Z12" t="n">
-        <v>600</v>
+        <v>686</v>
       </c>
       <c r="AA12" t="n">
-        <v>1465</v>
+        <v>1687</v>
       </c>
       <c r="AB12" t="n">
-        <v>771.2691</v>
+        <v>873.6539</v>
       </c>
       <c r="AC12" t="n">
-        <v>1904.32</v>
+        <v>2015.19</v>
       </c>
       <c r="AD12" t="n">
         <v>14</v>
       </c>
       <c r="AE12" t="n">
+        <v>22</v>
+      </c>
+      <c r="AF12" t="n">
         <v>25</v>
       </c>
-      <c r="AF12" t="n">
-        <v>24</v>
-      </c>
       <c r="AG12" t="n">
-        <v>6.7003</v>
+        <v>7.4169</v>
       </c>
     </row>
     <row r="13">
@@ -3495,22 +3575,22 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="M13" t="n">
-        <v>536</v>
+        <v>601</v>
       </c>
       <c r="N13" t="n">
-        <v>1242</v>
+        <v>1342</v>
       </c>
       <c r="O13" t="n">
-        <v>1773.1829</v>
+        <v>1454.2123</v>
       </c>
       <c r="P13" t="n">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="Q13" t="n">
-        <v>23.0283</v>
+        <v>20.4819</v>
       </c>
       <c r="R13" t="n">
         <v>422.9777</v>
@@ -3528,37 +3608,37 @@
         <v>1</v>
       </c>
       <c r="W13" t="n">
-        <v>0.04071401</v>
+        <v>0.04565135</v>
       </c>
       <c r="X13" t="n">
-        <v>0.04139862</v>
+        <v>0.04473184</v>
       </c>
       <c r="Y13" t="n">
-        <v>3.7827</v>
+        <v>3.0734</v>
       </c>
       <c r="Z13" t="n">
-        <v>404</v>
+        <v>530</v>
       </c>
       <c r="AA13" t="n">
-        <v>839</v>
+        <v>1121</v>
       </c>
       <c r="AB13" t="n">
-        <v>591.4457</v>
+        <v>674.2864</v>
       </c>
       <c r="AC13" t="n">
-        <v>1381.8448</v>
+        <v>1515.7981</v>
       </c>
       <c r="AD13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AE13" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AF13" t="n">
         <v>15</v>
       </c>
       <c r="AG13" t="n">
-        <v>6.0764</v>
+        <v>7.1869</v>
       </c>
     </row>
     <row r="14">
@@ -3596,22 +3676,22 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="M14" t="n">
-        <v>575</v>
+        <v>608</v>
       </c>
       <c r="N14" t="n">
-        <v>1251</v>
+        <v>1318</v>
       </c>
       <c r="O14" t="n">
-        <v>2728.8561</v>
+        <v>2719.246</v>
       </c>
       <c r="P14" t="n">
-        <v>112</v>
+        <v>135</v>
       </c>
       <c r="Q14" t="n">
-        <v>24.3648</v>
+        <v>20.1426</v>
       </c>
       <c r="R14" t="n">
         <v>379.8478</v>
@@ -3629,37 +3709,37 @@
         <v>1</v>
       </c>
       <c r="W14" t="n">
-        <v>0.04324609</v>
+        <v>0.04572804</v>
       </c>
       <c r="X14" t="n">
-        <v>0.03896225</v>
+        <v>0.04104896</v>
       </c>
       <c r="Y14" t="n">
-        <v>3.4224</v>
+        <v>4.2122</v>
       </c>
       <c r="Z14" t="n">
-        <v>511</v>
+        <v>570</v>
       </c>
       <c r="AA14" t="n">
-        <v>997</v>
+        <v>1215</v>
       </c>
       <c r="AB14" t="n">
-        <v>657.4996</v>
+        <v>688.6711</v>
       </c>
       <c r="AC14" t="n">
-        <v>1425.0113</v>
+        <v>1491.8692</v>
       </c>
       <c r="AD14" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AE14" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AF14" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AG14" t="n">
-        <v>6.6186</v>
+        <v>7.6692</v>
       </c>
     </row>
     <row r="15">
@@ -3697,22 +3777,22 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M15" t="n">
-        <v>275</v>
+        <v>318</v>
       </c>
       <c r="N15" t="n">
-        <v>789</v>
+        <v>855</v>
       </c>
       <c r="O15" t="n">
-        <v>1305.1535</v>
+        <v>2138.9962</v>
       </c>
       <c r="P15" t="n">
-        <v>40</v>
+        <v>74</v>
       </c>
       <c r="Q15" t="n">
-        <v>32.6288</v>
+        <v>28.9054</v>
       </c>
       <c r="R15" t="n">
         <v>217.9239</v>
@@ -3730,37 +3810,37 @@
         <v>1</v>
       </c>
       <c r="W15" t="n">
-        <v>0.03114383</v>
+        <v>0.03601359</v>
       </c>
       <c r="X15" t="n">
-        <v>0.03432524</v>
+        <v>0.03719655</v>
       </c>
       <c r="Y15" t="n">
-        <v>3.2121</v>
+        <v>2.7533</v>
       </c>
       <c r="Z15" t="n">
-        <v>160</v>
+        <v>227</v>
       </c>
       <c r="AA15" t="n">
-        <v>377</v>
+        <v>546</v>
       </c>
       <c r="AB15" t="n">
-        <v>306.4508</v>
+        <v>358.9066</v>
       </c>
       <c r="AC15" t="n">
-        <v>890.4529</v>
+        <v>969.4945</v>
       </c>
       <c r="AD15" t="n">
         <v>5</v>
       </c>
       <c r="AE15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AF15" t="n">
         <v>14</v>
       </c>
       <c r="AG15" t="n">
-        <v>6.1517</v>
+        <v>6.6409</v>
       </c>
     </row>
     <row r="16">
@@ -3798,22 +3878,22 @@
         <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M16" t="n">
-        <v>261</v>
+        <v>274</v>
       </c>
       <c r="N16" t="n">
-        <v>668</v>
+        <v>679</v>
       </c>
       <c r="O16" t="n">
-        <v>839.4407</v>
+        <v>862.997</v>
       </c>
       <c r="P16" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="Q16" t="n">
-        <v>20.986</v>
+        <v>19.6136</v>
       </c>
       <c r="R16" t="n">
         <v>332.8944</v>
@@ -3831,37 +3911,37 @@
         <v>0.7919</v>
       </c>
       <c r="W16" t="n">
-        <v>0.02484531</v>
+        <v>0.02608282</v>
       </c>
       <c r="X16" t="n">
-        <v>0.02806015</v>
+        <v>0.02852222</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.2016</v>
+        <v>1.502</v>
       </c>
       <c r="Z16" t="n">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="AA16" t="n">
-        <v>271</v>
+        <v>280</v>
       </c>
       <c r="AB16" t="n">
-        <v>287.9655</v>
+        <v>305.5219</v>
       </c>
       <c r="AC16" t="n">
-        <v>739.4285</v>
+        <v>756.8133</v>
       </c>
       <c r="AD16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE16" t="n">
         <v>9</v>
       </c>
       <c r="AF16" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AG16" t="n">
-        <v>6.7114</v>
+        <v>7.6559</v>
       </c>
     </row>
     <row r="17">
@@ -3899,22 +3979,22 @@
         <v>1</v>
       </c>
       <c r="L17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M17" t="n">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="N17" t="n">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="O17" t="n">
-        <v>107.3259</v>
+        <v>63.4558</v>
       </c>
       <c r="P17" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Q17" t="n">
-        <v>13.4157</v>
+        <v>10.576</v>
       </c>
       <c r="R17" t="n">
         <v>205.7756</v>
@@ -3932,37 +4012,117 @@
         <v>0.714</v>
       </c>
       <c r="W17" t="n">
-        <v>0.0203961</v>
+        <v>0.02113509</v>
       </c>
       <c r="X17" t="n">
-        <v>0.02989546</v>
+        <v>0.03020114</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.9439</v>
+        <v>1.4579</v>
       </c>
       <c r="Z17" t="n">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="AA17" t="n">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="AB17" t="n">
-        <v>152.7107</v>
+        <v>158.5391</v>
       </c>
       <c r="AC17" t="n">
-        <v>540.3036</v>
+        <v>546.1319999999999</v>
       </c>
       <c r="AD17" t="n">
         <v>4</v>
       </c>
       <c r="AE17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF17" t="n">
         <v>6</v>
       </c>
       <c r="AG17" t="n">
-        <v>4.7971</v>
+        <v>5.6111</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="I18" t="n">
+        <v>368.3785</v>
+      </c>
+      <c r="J18" t="n">
+        <v>576.7477</v>
+      </c>
+      <c r="K18" t="b">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>3</v>
+      </c>
+      <c r="M18" t="n">
+        <v>154</v>
+      </c>
+      <c r="N18" t="n">
+        <v>236</v>
+      </c>
+      <c r="O18" t="n">
+        <v>209.9828</v>
+      </c>
+      <c r="P18" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>14.9988</v>
+      </c>
+      <c r="R18" t="n">
+        <v>56.8701</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3677</v>
+      </c>
+      <c r="T18" t="n">
+        <v>7091</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0.04188197</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0.03328162</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>5.2752</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>108</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>124</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>167.8112</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>258.1665</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>7.5189</v>
       </c>
     </row>
   </sheetData>

--- a/results/542_z06/5_quantification/542_z06_quantification.xlsx
+++ b/results/542_z06/5_quantification/542_z06_quantification.xlsx
@@ -460,13 +460,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
@@ -525,13 +525,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2541.7692</v>
+        <v>2576</v>
       </c>
       <c r="D6" t="n">
         <v>3013</v>
       </c>
       <c r="E6" t="n">
-        <v>1427.4432</v>
+        <v>1380.4162</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -539,7 +539,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7">
@@ -554,13 +554,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>108.2371</v>
+        <v>109.5668</v>
       </c>
       <c r="D7" t="n">
         <v>124.4642</v>
       </c>
       <c r="E7" t="n">
-        <v>40.2415</v>
+        <v>38.2072</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -568,7 +568,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8">
@@ -583,13 +583,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>31.7238</v>
+        <v>31.8891</v>
       </c>
       <c r="D8" t="n">
         <v>33.1799</v>
       </c>
       <c r="E8" t="n">
-        <v>10.2747</v>
+        <v>10.1914</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -597,7 +597,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
@@ -612,13 +612,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3.5771</v>
+        <v>3.6142</v>
       </c>
       <c r="D9" t="n">
         <v>3.6285</v>
       </c>
       <c r="E9" t="n">
-        <v>1.3089</v>
+        <v>1.2579</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10">
@@ -641,13 +641,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.9409</v>
       </c>
       <c r="D10" t="n">
         <v>0.9613</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0596</v>
+        <v>0.0498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -655,7 +655,7 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11">
@@ -670,13 +670,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.7472</v>
+        <v>0.7493</v>
       </c>
       <c r="D11" t="n">
         <v>0.7672</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1322</v>
+        <v>0.1286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -684,7 +684,7 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12">
@@ -699,13 +699,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>11</v>
+        <v>11.4</v>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E12" t="n">
-        <v>5.8045</v>
+        <v>5.5395</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13">
@@ -728,13 +728,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>433.1429</v>
+        <v>447.6667</v>
       </c>
       <c r="D13" t="n">
-        <v>399</v>
+        <v>410</v>
       </c>
       <c r="E13" t="n">
-        <v>196.8294</v>
+        <v>188.7363</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14">
@@ -757,13 +757,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>995.9286</v>
+        <v>1016.0667</v>
       </c>
       <c r="D14" t="n">
-        <v>923.5</v>
+        <v>960</v>
       </c>
       <c r="E14" t="n">
-        <v>437.7301</v>
+        <v>429.4384</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15">
@@ -786,13 +786,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2104.0271</v>
+        <v>1985.4972</v>
       </c>
       <c r="D15" t="n">
-        <v>1924.3028</v>
+        <v>1456.1535</v>
       </c>
       <c r="E15" t="n">
-        <v>1562.1019</v>
+        <v>1542.2566</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16">
@@ -815,13 +815,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>92.28570000000001</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="D16" t="n">
-        <v>78.5</v>
+        <v>71</v>
       </c>
       <c r="E16" t="n">
-        <v>70.267</v>
+        <v>68.8319</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17">
@@ -844,13 +844,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>22.7907</v>
+        <v>22.4624</v>
       </c>
       <c r="D17" t="n">
-        <v>22.6947</v>
+        <v>22.5506</v>
       </c>
       <c r="E17" t="n">
-        <v>4.1278</v>
+        <v>3.8372</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18">
@@ -873,13 +873,13 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>280.6021</v>
+        <v>292.0698</v>
       </c>
       <c r="D18" t="n">
-        <v>305.9864</v>
+        <v>309.5219</v>
       </c>
       <c r="E18" t="n">
-        <v>127.9813</v>
+        <v>122.8085</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19">
@@ -902,13 +902,13 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>10209.4286</v>
+        <v>10491.4667</v>
       </c>
       <c r="D19" t="n">
-        <v>11138.5</v>
+        <v>11337</v>
       </c>
       <c r="E19" t="n">
-        <v>3432.1456</v>
+        <v>3304.0289</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20">
@@ -931,13 +931,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>23888.4286</v>
+        <v>24400.8667</v>
       </c>
       <c r="D20" t="n">
-        <v>25904.5</v>
+        <v>26961</v>
       </c>
       <c r="E20" t="n">
-        <v>7904.5602</v>
+        <v>7815.1597</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21">
@@ -966,7 +966,7 @@
         <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22">
@@ -989,13 +989,13 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.9913999999999999</v>
+        <v>0.9858</v>
       </c>
       <c r="D22" t="n">
         <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0263</v>
+        <v>0.0377</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.04140095</v>
+        <v>0.04176754</v>
       </c>
       <c r="D23" t="n">
-        <v>0.04064855</v>
+        <v>0.04188197</v>
       </c>
       <c r="E23" t="n">
-        <v>0.00716751</v>
+        <v>0.00694049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24">
@@ -1047,13 +1047,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.04048473</v>
+        <v>0.04050161</v>
       </c>
       <c r="D24" t="n">
-        <v>0.03924596</v>
+        <v>0.03974318</v>
       </c>
       <c r="E24" t="n">
-        <v>0.00640785</v>
+        <v>0.00624729</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25">
@@ -1076,13 +1076,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>4.0757</v>
+        <v>4.05</v>
       </c>
       <c r="D25" t="n">
-        <v>4.0826</v>
+        <v>3.953</v>
       </c>
       <c r="E25" t="n">
-        <v>1.2805</v>
+        <v>1.2415</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="26">
@@ -1105,13 +1105,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>379.2857</v>
+        <v>392.8667</v>
       </c>
       <c r="D26" t="n">
-        <v>335</v>
+        <v>351</v>
       </c>
       <c r="E26" t="n">
-        <v>202.6245</v>
+        <v>192.4596</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27">
@@ -1134,13 +1134,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>789</v>
+        <v>810.2</v>
       </c>
       <c r="D27" t="n">
-        <v>619</v>
+        <v>691</v>
       </c>
       <c r="E27" t="n">
-        <v>478.9541</v>
+        <v>449.1893</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="28">
@@ -1163,13 +1163,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>492.1853</v>
+        <v>509.1242</v>
       </c>
       <c r="D28" t="n">
-        <v>450.9544</v>
+        <v>464.262</v>
       </c>
       <c r="E28" t="n">
-        <v>225.1756</v>
+        <v>216.7054</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="29">
@@ -1192,13 +1192,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1128.49</v>
+        <v>1153.1702</v>
       </c>
       <c r="D29" t="n">
-        <v>1034.4651</v>
+        <v>1075.2641</v>
       </c>
       <c r="E29" t="n">
-        <v>500.3153</v>
+        <v>492.4521</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="30">
@@ -1221,13 +1221,13 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>9.357100000000001</v>
+        <v>9.6</v>
       </c>
       <c r="D30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E30" t="n">
-        <v>5.078</v>
+        <v>4.8077</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="31">
@@ -1250,13 +1250,13 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>13.1429</v>
+        <v>13.2667</v>
       </c>
       <c r="D31" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E31" t="n">
-        <v>5.4187</v>
+        <v>5.3515</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="32">
@@ -1279,13 +1279,13 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>13.2143</v>
+        <v>13.8667</v>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="E32" t="n">
-        <v>5.7536</v>
+        <v>5.2762</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="33">
@@ -1308,13 +1308,13 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>7.4897</v>
+        <v>7.5373</v>
       </c>
       <c r="D33" t="n">
-        <v>7.4857</v>
+        <v>7.5189</v>
       </c>
       <c r="E33" t="n">
-        <v>0.4228</v>
+        <v>0.3988</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -1373,7 +1373,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1008847</v>
+        <v>1006403</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>39263</v>
+        <v>39224</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.03891869</v>
+        <v>0.03897445</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>863</v>
+        <v>869</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.00085543</v>
+        <v>0.00086347</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1.685e-05</v>
+        <v>1.888e-05</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>158.3185</v>
+        <v>156.896</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>25</v>
+        <v>25.5</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.04408455</v>
+        <v>0.0441484</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.03886559</v>
+        <v>0.03892297</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1630,7 +1630,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>362</v>
+        <v>375</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1670,7 +1670,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.03891869</v>
+        <v>0.03897445</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.03927751</v>
+        <v>0.03934706</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8.154500000000001</v>
+        <v>8.1572</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>5.6569</v>
+        <v>4.4721</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>38017</v>
+        <v>37978</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>694</v>
+        <v>725</v>
       </c>
     </row>
     <row r="9">
@@ -1984,7 +1984,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>15.5058</v>
+        <v>13.8354</v>
       </c>
     </row>
     <row r="10">
@@ -2014,7 +2014,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>36.7054</v>
+        <v>33.7291</v>
       </c>
     </row>
     <row r="12">
@@ -2044,7 +2044,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.2493</v>
+        <v>0.2041</v>
       </c>
     </row>
     <row r="14">
@@ -2059,7 +2059,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.7507</v>
+        <v>0.7959000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -2106,7 +2106,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18">
@@ -2121,7 +2121,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19">
@@ -2230,7 +2230,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.7354000000000001</v>
+        <v>0.5814</v>
       </c>
     </row>
     <row r="26">
@@ -2259,7 +2259,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG18"/>
+  <dimension ref="A1:AG20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2636,100 +2636,100 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>556</v>
+        <v>1001</v>
       </c>
       <c r="C4" t="n">
-        <v>44.867</v>
+        <v>62.1533</v>
       </c>
       <c r="D4" t="n">
-        <v>25.9744</v>
+        <v>28.1242</v>
       </c>
       <c r="E4" t="n">
-        <v>1.7274</v>
+        <v>2.21</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8154</v>
+        <v>0.8918</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5265</v>
+        <v>0.5533</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.4071</v>
+        <v>-0.1968</v>
       </c>
       <c r="I4" t="n">
-        <v>66.9281</v>
+        <v>55.7832</v>
       </c>
       <c r="J4" t="n">
-        <v>106.1025</v>
+        <v>107.9491</v>
       </c>
       <c r="K4" t="b">
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>10</v>
+      </c>
+      <c r="M4" t="n">
+        <v>368</v>
+      </c>
+      <c r="N4" t="n">
+        <v>687</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1456.1535</v>
+      </c>
+      <c r="P4" t="n">
+        <v>53</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>27.4746</v>
+      </c>
+      <c r="R4" t="n">
+        <v>225.3087</v>
+      </c>
+      <c r="S4" t="n">
+        <v>8379</v>
+      </c>
+      <c r="T4" t="n">
+        <v>19327</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.884</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.04391932</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.03554613</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>4.4384</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>308</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>632</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>423.9899</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>782.2397</v>
+      </c>
+      <c r="AD4" t="n">
         <v>7</v>
       </c>
-      <c r="M4" t="n">
-        <v>281</v>
-      </c>
-      <c r="N4" t="n">
-        <v>689</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1352.2834</v>
-      </c>
-      <c r="P4" t="n">
-        <v>46</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>29.3975</v>
-      </c>
-      <c r="R4" t="n">
-        <v>160.6396</v>
-      </c>
-      <c r="S4" t="n">
-        <v>6976</v>
-      </c>
-      <c r="T4" t="n">
-        <v>18799</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0.9774</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0.04028096</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0.03665089</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>4.3576</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>210</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>367</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>327.8772</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>786.8964999999999</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>5</v>
-      </c>
       <c r="AE4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AF4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AG4" t="n">
-        <v>7.1332</v>
+        <v>7.6771</v>
       </c>
     </row>
     <row r="5">
@@ -3177,16 +3177,16 @@
         <v>459</v>
       </c>
       <c r="N9" t="n">
-        <v>887</v>
+        <v>883</v>
       </c>
       <c r="O9" t="n">
-        <v>1793.0063</v>
+        <v>919.9675999999999</v>
       </c>
       <c r="P9" t="n">
-        <v>83</v>
+        <v>44</v>
       </c>
       <c r="Q9" t="n">
-        <v>21.6025</v>
+        <v>20.9084</v>
       </c>
       <c r="R9" t="n">
         <v>359.1909</v>
@@ -3195,7 +3195,7 @@
         <v>12383</v>
       </c>
       <c r="T9" t="n">
-        <v>27034</v>
+        <v>26961</v>
       </c>
       <c r="U9" t="n">
         <v>1</v>
@@ -3207,7 +3207,7 @@
         <v>0.03706695</v>
       </c>
       <c r="X9" t="n">
-        <v>0.03281053</v>
+        <v>0.03275101</v>
       </c>
       <c r="Y9" t="n">
         <v>3.8976</v>
@@ -3222,7 +3222,7 @@
         <v>514.3036</v>
       </c>
       <c r="AC9" t="n">
-        <v>993.6661</v>
+        <v>987.4234</v>
       </c>
       <c r="AD9" t="n">
         <v>10</v>
@@ -3382,13 +3382,13 @@
         <v>1270</v>
       </c>
       <c r="O11" t="n">
-        <v>3369.3191</v>
+        <v>3280.2775</v>
       </c>
       <c r="P11" t="n">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="Q11" t="n">
-        <v>24.4154</v>
+        <v>24.4797</v>
       </c>
       <c r="R11" t="n">
         <v>309.5219</v>
@@ -4050,40 +4050,40 @@
         <v>17</v>
       </c>
       <c r="I18" t="n">
-        <v>368.3785</v>
+        <v>310.7538</v>
       </c>
       <c r="J18" t="n">
-        <v>576.7477</v>
+        <v>226.5389</v>
       </c>
       <c r="K18" t="b">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="M18" t="n">
-        <v>154</v>
+        <v>564</v>
       </c>
       <c r="N18" t="n">
-        <v>236</v>
+        <v>1304</v>
       </c>
       <c r="O18" t="n">
-        <v>209.9828</v>
+        <v>1184.2885</v>
       </c>
       <c r="P18" t="n">
-        <v>14</v>
+        <v>58</v>
       </c>
       <c r="Q18" t="n">
-        <v>14.9988</v>
+        <v>20.4188</v>
       </c>
       <c r="R18" t="n">
-        <v>56.8701</v>
+        <v>387.9483</v>
       </c>
       <c r="S18" t="n">
-        <v>3677</v>
+        <v>13037</v>
       </c>
       <c r="T18" t="n">
-        <v>7091</v>
+        <v>31120</v>
       </c>
       <c r="U18" t="n">
         <v>1</v>
@@ -4092,36 +4092,196 @@
         <v>1</v>
       </c>
       <c r="W18" t="n">
+        <v>0.04326149</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0.04190231</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>3.6087</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>485</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>842</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>650.1564</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1509.5921</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>16</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>7.6596</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="I19" t="n">
+        <v>933.6445</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3.9103</v>
+      </c>
+      <c r="K19" t="b">
+        <v>1</v>
+      </c>
+      <c r="L19" t="n">
+        <v>2</v>
+      </c>
+      <c r="M19" t="n">
+        <v>69</v>
+      </c>
+      <c r="N19" t="n">
+        <v>189</v>
+      </c>
+      <c r="O19" t="n">
+        <v>389.9483</v>
+      </c>
+      <c r="P19" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>21.6638</v>
+      </c>
+      <c r="R19" t="n">
+        <v>87.0061</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2915</v>
+      </c>
+      <c r="T19" t="n">
+        <v>8653</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0.5433</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0.5282</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0.02367067</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0.02184214</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>2.2987</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>97</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>79.7696</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>213.267</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>8.4397</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="I20" t="n">
+        <v>368.3785</v>
+      </c>
+      <c r="J20" t="n">
+        <v>576.7477</v>
+      </c>
+      <c r="K20" t="b">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>3</v>
+      </c>
+      <c r="M20" t="n">
+        <v>154</v>
+      </c>
+      <c r="N20" t="n">
+        <v>236</v>
+      </c>
+      <c r="O20" t="n">
+        <v>209.9828</v>
+      </c>
+      <c r="P20" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>14.9988</v>
+      </c>
+      <c r="R20" t="n">
+        <v>56.8701</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3677</v>
+      </c>
+      <c r="T20" t="n">
+        <v>7091</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1</v>
+      </c>
+      <c r="W20" t="n">
         <v>0.04188197</v>
       </c>
-      <c r="X18" t="n">
+      <c r="X20" t="n">
         <v>0.03328162</v>
       </c>
-      <c r="Y18" t="n">
+      <c r="Y20" t="n">
         <v>5.2752</v>
       </c>
-      <c r="Z18" t="n">
+      <c r="Z20" t="n">
         <v>108</v>
       </c>
-      <c r="AA18" t="n">
+      <c r="AA20" t="n">
         <v>124</v>
       </c>
-      <c r="AB18" t="n">
+      <c r="AB20" t="n">
         <v>167.8112</v>
       </c>
-      <c r="AC18" t="n">
+      <c r="AC20" t="n">
         <v>258.1665</v>
       </c>
-      <c r="AD18" t="n">
+      <c r="AD20" t="n">
         <v>2</v>
       </c>
-      <c r="AE18" t="n">
+      <c r="AE20" t="n">
         <v>5</v>
       </c>
-      <c r="AF18" t="n">
+      <c r="AF20" t="n">
         <v>6</v>
       </c>
-      <c r="AG18" t="n">
+      <c r="AG20" t="n">
         <v>7.5189</v>
       </c>
     </row>

--- a/results/542_z06/5_quantification/542_z06_quantification.xlsx
+++ b/results/542_z06/5_quantification/542_z06_quantification.xlsx
@@ -699,13 +699,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>11.4</v>
+        <v>14.0667</v>
       </c>
       <c r="D12" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E12" t="n">
-        <v>5.5395</v>
+        <v>6.4195</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -786,13 +786,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1985.4972</v>
+        <v>2004.9549</v>
       </c>
       <c r="D15" t="n">
-        <v>1456.1535</v>
+        <v>2091.6286</v>
       </c>
       <c r="E15" t="n">
-        <v>1542.2566</v>
+        <v>1454.7884</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -815,13 +815,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>87.59999999999999</v>
+        <v>88.7333</v>
       </c>
       <c r="D16" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="E16" t="n">
-        <v>68.8319</v>
+        <v>65.1662</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -844,13 +844,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>22.4624</v>
+        <v>22.4129</v>
       </c>
       <c r="D17" t="n">
-        <v>22.5506</v>
+        <v>22.7351</v>
       </c>
       <c r="E17" t="n">
-        <v>3.8372</v>
+        <v>3.7601</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1076,13 +1076,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>4.05</v>
+        <v>5.0246</v>
       </c>
       <c r="D25" t="n">
-        <v>3.953</v>
+        <v>4.7443</v>
       </c>
       <c r="E25" t="n">
-        <v>1.2415</v>
+        <v>1.3785</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1308,13 +1308,13 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>7.5373</v>
+        <v>7.5443</v>
       </c>
       <c r="D33" t="n">
         <v>7.5189</v>
       </c>
       <c r="E33" t="n">
-        <v>0.3988</v>
+        <v>0.4181</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>39224</v>
+        <v>39229</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.03897445</v>
+        <v>0.03897941</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>156.896</v>
+        <v>156.916</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>25.5</v>
+        <v>26</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.0441484</v>
+        <v>0.04415419</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.03892297</v>
+        <v>0.0389281</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1670,7 +1670,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.03897445</v>
+        <v>0.03897941</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.03934706</v>
+        <v>0.03935203</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8.1572</v>
+        <v>8.1584</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>37978</v>
+        <v>37983</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>725</v>
+        <v>727</v>
       </c>
     </row>
     <row r="9">
@@ -1984,7 +1984,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>13.8354</v>
+        <v>13.6739</v>
       </c>
     </row>
     <row r="10">
@@ -2014,7 +2014,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>33.7291</v>
+        <v>33.7004</v>
       </c>
     </row>
     <row r="12">
@@ -2044,7 +2044,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.2041</v>
+        <v>0.2036</v>
       </c>
     </row>
     <row r="14">
@@ -2059,7 +2059,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.7959000000000001</v>
+        <v>0.7964</v>
       </c>
     </row>
     <row r="15">
@@ -2121,7 +2121,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19">
@@ -2136,7 +2136,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
     </row>
     <row r="21">
@@ -2464,7 +2464,7 @@
         <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M2" t="n">
         <v>218</v>
@@ -2503,7 +2503,7 @@
         <v>0.04576965</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.7877</v>
+        <v>3.2523</v>
       </c>
       <c r="Z2" t="n">
         <v>218</v>
@@ -2666,7 +2666,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="M4" t="n">
         <v>368</v>
@@ -2705,7 +2705,7 @@
         <v>0.03554613</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.4384</v>
+        <v>5.7699</v>
       </c>
       <c r="Z4" t="n">
         <v>308</v>
@@ -2767,7 +2767,7 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M5" t="n">
         <v>255</v>
@@ -2806,7 +2806,7 @@
         <v>0.04288232</v>
       </c>
       <c r="Y5" t="n">
-        <v>3.953</v>
+        <v>5.9296</v>
       </c>
       <c r="Z5" t="n">
         <v>211</v>
@@ -2868,7 +2868,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="M6" t="n">
         <v>380</v>
@@ -2877,13 +2877,13 @@
         <v>1031</v>
       </c>
       <c r="O6" t="n">
-        <v>2055.5992</v>
+        <v>2222.3099</v>
       </c>
       <c r="P6" t="n">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="Q6" t="n">
-        <v>24.4714</v>
+        <v>22.9104</v>
       </c>
       <c r="R6" t="n">
         <v>322.0427</v>
@@ -2907,7 +2907,7 @@
         <v>0.03594213</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.1736</v>
+        <v>3.1052</v>
       </c>
       <c r="Z6" t="n">
         <v>319</v>
@@ -2969,7 +2969,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="M7" t="n">
         <v>784</v>
@@ -2978,13 +2978,13 @@
         <v>1661</v>
       </c>
       <c r="O7" t="n">
-        <v>5837.1021</v>
+        <v>5469.8939</v>
       </c>
       <c r="P7" t="n">
-        <v>238</v>
+        <v>222</v>
       </c>
       <c r="Q7" t="n">
-        <v>24.5256</v>
+        <v>24.6392</v>
       </c>
       <c r="R7" t="n">
         <v>438.5168</v>
@@ -3008,7 +3008,7 @@
         <v>0.05253669</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.0169</v>
+        <v>6.1571</v>
       </c>
       <c r="Z7" t="n">
         <v>781</v>
@@ -3070,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M8" t="n">
         <v>410</v>
@@ -3109,7 +3109,7 @@
         <v>0.03974318</v>
       </c>
       <c r="Y8" t="n">
-        <v>6.6061</v>
+        <v>7.5499</v>
       </c>
       <c r="Z8" t="n">
         <v>351</v>
@@ -3171,7 +3171,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="M9" t="n">
         <v>459</v>
@@ -3210,7 +3210,7 @@
         <v>0.03275101</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.8976</v>
+        <v>4.7329</v>
       </c>
       <c r="Z9" t="n">
         <v>415</v>
@@ -3272,7 +3272,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M10" t="n">
         <v>388</v>
@@ -3281,13 +3281,13 @@
         <v>960</v>
       </c>
       <c r="O10" t="n">
-        <v>2255.055</v>
+        <v>2091.6286</v>
       </c>
       <c r="P10" t="n">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="Q10" t="n">
-        <v>22.5506</v>
+        <v>22.7351</v>
       </c>
       <c r="R10" t="n">
         <v>302.4508</v>
@@ -3311,7 +3311,7 @@
         <v>0.03874874</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.9838</v>
+        <v>2.3144</v>
       </c>
       <c r="Z10" t="n">
         <v>301</v>
@@ -3335,7 +3335,7 @@
         <v>12</v>
       </c>
       <c r="AG10" t="n">
-        <v>8.5387</v>
+        <v>8.643700000000001</v>
       </c>
     </row>
     <row r="11">
@@ -3373,7 +3373,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M11" t="n">
         <v>465</v>
@@ -3412,7 +3412,7 @@
         <v>0.04489854</v>
       </c>
       <c r="Y11" t="n">
-        <v>5.1693</v>
+        <v>5.4923</v>
       </c>
       <c r="Z11" t="n">
         <v>444</v>
@@ -3474,7 +3474,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="M12" t="n">
         <v>767</v>
@@ -3483,13 +3483,13 @@
         <v>1786</v>
       </c>
       <c r="O12" t="n">
-        <v>4279.8309</v>
+        <v>4088.0908</v>
       </c>
       <c r="P12" t="n">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="Q12" t="n">
-        <v>19.1064</v>
+        <v>19.0144</v>
       </c>
       <c r="R12" t="n">
         <v>468.2742</v>
@@ -3513,7 +3513,7 @@
         <v>0.05238151</v>
       </c>
       <c r="Y12" t="n">
-        <v>3.8439</v>
+        <v>4.271</v>
       </c>
       <c r="Z12" t="n">
         <v>686</v>
@@ -3575,7 +3575,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="M13" t="n">
         <v>601</v>
@@ -3584,13 +3584,13 @@
         <v>1342</v>
       </c>
       <c r="O13" t="n">
-        <v>1454.2123</v>
+        <v>2217.9007</v>
       </c>
       <c r="P13" t="n">
-        <v>71</v>
+        <v>106</v>
       </c>
       <c r="Q13" t="n">
-        <v>20.4819</v>
+        <v>20.9236</v>
       </c>
       <c r="R13" t="n">
         <v>422.9777</v>
@@ -3614,7 +3614,7 @@
         <v>0.04473184</v>
       </c>
       <c r="Y13" t="n">
-        <v>3.0734</v>
+        <v>4.492</v>
       </c>
       <c r="Z13" t="n">
         <v>530</v>
@@ -3676,7 +3676,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="M14" t="n">
         <v>608</v>
@@ -3685,13 +3685,13 @@
         <v>1318</v>
       </c>
       <c r="O14" t="n">
-        <v>2719.246</v>
+        <v>2788.4297</v>
       </c>
       <c r="P14" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="Q14" t="n">
-        <v>20.1426</v>
+        <v>20.5032</v>
       </c>
       <c r="R14" t="n">
         <v>379.8478</v>
@@ -3715,7 +3715,7 @@
         <v>0.04104896</v>
       </c>
       <c r="Y14" t="n">
-        <v>4.2122</v>
+        <v>5.2653</v>
       </c>
       <c r="Z14" t="n">
         <v>570</v>
@@ -3777,7 +3777,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M15" t="n">
         <v>318</v>
@@ -3786,13 +3786,13 @@
         <v>855</v>
       </c>
       <c r="O15" t="n">
-        <v>2138.9962</v>
+        <v>2153.653</v>
       </c>
       <c r="P15" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q15" t="n">
-        <v>28.9054</v>
+        <v>28.7154</v>
       </c>
       <c r="R15" t="n">
         <v>217.9239</v>
@@ -3816,7 +3816,7 @@
         <v>0.03719655</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.7533</v>
+        <v>4.1299</v>
       </c>
       <c r="Z15" t="n">
         <v>227</v>
@@ -3878,7 +3878,7 @@
         <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M16" t="n">
         <v>274</v>
@@ -3917,7 +3917,7 @@
         <v>0.02852222</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.502</v>
+        <v>1.8024</v>
       </c>
       <c r="Z16" t="n">
         <v>187</v>
@@ -3979,22 +3979,22 @@
         <v>1</v>
       </c>
       <c r="L17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M17" t="n">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="N17" t="n">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="O17" t="n">
-        <v>63.4558</v>
+        <v>95.4264</v>
       </c>
       <c r="P17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q17" t="n">
-        <v>10.576</v>
+        <v>13.6323</v>
       </c>
       <c r="R17" t="n">
         <v>205.7756</v>
@@ -4012,25 +4012,25 @@
         <v>0.714</v>
       </c>
       <c r="W17" t="n">
-        <v>0.02113509</v>
+        <v>0.02187408</v>
       </c>
       <c r="X17" t="n">
-        <v>0.03020114</v>
+        <v>0.03050682</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.4579</v>
+        <v>2.4298</v>
       </c>
       <c r="Z17" t="n">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="AA17" t="n">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="AB17" t="n">
-        <v>158.5391</v>
+        <v>164.3675</v>
       </c>
       <c r="AC17" t="n">
-        <v>546.1319999999999</v>
+        <v>551.9605</v>
       </c>
       <c r="AD17" t="n">
         <v>4</v>
@@ -4042,7 +4042,7 @@
         <v>6</v>
       </c>
       <c r="AG17" t="n">
-        <v>5.6111</v>
+        <v>5.8635</v>
       </c>
     </row>
     <row r="18">
@@ -4059,7 +4059,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="M18" t="n">
         <v>564</v>
@@ -4098,7 +4098,7 @@
         <v>0.04190231</v>
       </c>
       <c r="Y18" t="n">
-        <v>3.6087</v>
+        <v>4.382</v>
       </c>
       <c r="Z18" t="n">
         <v>485</v>
@@ -4219,7 +4219,7 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M20" t="n">
         <v>154</v>
@@ -4258,7 +4258,7 @@
         <v>0.03328162</v>
       </c>
       <c r="Y20" t="n">
-        <v>5.2752</v>
+        <v>7.0336</v>
       </c>
       <c r="Z20" t="n">
         <v>108</v>

--- a/results/542_z06/5_quantification/542_z06_quantification.xlsx
+++ b/results/542_z06/5_quantification/542_z06_quantification.xlsx
@@ -699,13 +699,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>14.0667</v>
+        <v>14.5333</v>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E12" t="n">
-        <v>6.4195</v>
+        <v>6.7809</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -728,13 +728,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>447.6667</v>
+        <v>473.2</v>
       </c>
       <c r="D13" t="n">
-        <v>410</v>
+        <v>423</v>
       </c>
       <c r="E13" t="n">
-        <v>188.7363</v>
+        <v>202.6359</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -757,13 +757,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1016.0667</v>
+        <v>1032.7333</v>
       </c>
       <c r="D14" t="n">
-        <v>960</v>
+        <v>981</v>
       </c>
       <c r="E14" t="n">
-        <v>429.4384</v>
+        <v>449.1294</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -786,13 +786,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2004.9549</v>
+        <v>2075.1267</v>
       </c>
       <c r="D15" t="n">
-        <v>2091.6286</v>
+        <v>2042.0723</v>
       </c>
       <c r="E15" t="n">
-        <v>1454.7884</v>
+        <v>1418.7375</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -815,13 +815,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>88.7333</v>
+        <v>93.33329999999999</v>
       </c>
       <c r="D16" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="E16" t="n">
-        <v>65.1662</v>
+        <v>65.4181</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -844,13 +844,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>22.4129</v>
+        <v>22.3671</v>
       </c>
       <c r="D17" t="n">
-        <v>22.7351</v>
+        <v>21.9229</v>
       </c>
       <c r="E17" t="n">
-        <v>3.7601</v>
+        <v>3.3454</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1018,13 +1018,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.04176754</v>
+        <v>0.04403868</v>
       </c>
       <c r="D23" t="n">
-        <v>0.04188197</v>
+        <v>0.04464217</v>
       </c>
       <c r="E23" t="n">
-        <v>0.00694049</v>
+        <v>0.00754502</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1047,13 +1047,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.04050161</v>
+        <v>0.04109938</v>
       </c>
       <c r="D24" t="n">
-        <v>0.03974318</v>
+        <v>0.04043298</v>
       </c>
       <c r="E24" t="n">
-        <v>0.00624729</v>
+        <v>0.00712237</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1076,13 +1076,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>5.0246</v>
+        <v>5.1783</v>
       </c>
       <c r="D25" t="n">
-        <v>4.7443</v>
+        <v>4.8462</v>
       </c>
       <c r="E25" t="n">
-        <v>1.3785</v>
+        <v>1.5065</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1105,13 +1105,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>392.8667</v>
+        <v>424.8667</v>
       </c>
       <c r="D26" t="n">
-        <v>351</v>
+        <v>364</v>
       </c>
       <c r="E26" t="n">
-        <v>192.4596</v>
+        <v>203.6341</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1134,13 +1134,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>810.2</v>
+        <v>852.9333</v>
       </c>
       <c r="D27" t="n">
-        <v>691</v>
+        <v>731</v>
       </c>
       <c r="E27" t="n">
-        <v>449.1893</v>
+        <v>472.5172</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1163,13 +1163,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>509.1242</v>
+        <v>538.1704</v>
       </c>
       <c r="D28" t="n">
-        <v>464.262</v>
+        <v>477.6762</v>
       </c>
       <c r="E28" t="n">
-        <v>216.7054</v>
+        <v>233.7423</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1192,13 +1192,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1153.1702</v>
+        <v>1172.3557</v>
       </c>
       <c r="D29" t="n">
-        <v>1075.2641</v>
+        <v>1098.9209</v>
       </c>
       <c r="E29" t="n">
-        <v>492.4521</v>
+        <v>516.3555</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1221,13 +1221,13 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>9.6</v>
+        <v>10.7333</v>
       </c>
       <c r="D30" t="n">
         <v>10</v>
       </c>
       <c r="E30" t="n">
-        <v>4.8077</v>
+        <v>5.7998</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1250,13 +1250,13 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>13.2667</v>
+        <v>13.1333</v>
       </c>
       <c r="D31" t="n">
         <v>14</v>
       </c>
       <c r="E31" t="n">
-        <v>5.3515</v>
+        <v>5.4362</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1279,13 +1279,13 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>13.8667</v>
+        <v>13.6</v>
       </c>
       <c r="D32" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E32" t="n">
-        <v>5.2762</v>
+        <v>5.4485</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1308,13 +1308,13 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>7.5443</v>
+        <v>7.4697</v>
       </c>
       <c r="D33" t="n">
-        <v>7.5189</v>
+        <v>7.5343</v>
       </c>
       <c r="E33" t="n">
-        <v>0.4181</v>
+        <v>0.4396</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>39229</v>
+        <v>39890</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.03897941</v>
+        <v>0.03963621</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>869</v>
+        <v>905</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.00086347</v>
+        <v>0.00089924</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>250</v>
+        <v>235</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>156.916</v>
+        <v>169.7447</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.04415419</v>
+        <v>0.0448956</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.0389281</v>
+        <v>0.03960452</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1670,7 +1670,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.03897941</v>
+        <v>0.03963621</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.03935203</v>
+        <v>0.04000882</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8.1584</v>
+        <v>8.1721</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>37983</v>
+        <v>38643</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>727</v>
+        <v>770</v>
       </c>
     </row>
     <row r="9">
@@ -1984,7 +1984,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>13.6739</v>
+        <v>13.5754</v>
       </c>
     </row>
     <row r="10">
@@ -1999,7 +1999,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.39</v>
+        <v>0.3677</v>
       </c>
     </row>
     <row r="11">
@@ -2014,7 +2014,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>33.7004</v>
+        <v>32.7814</v>
       </c>
     </row>
     <row r="12">
@@ -2044,7 +2044,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.2036</v>
+        <v>0.1753</v>
       </c>
     </row>
     <row r="14">
@@ -2059,7 +2059,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.7964</v>
+        <v>0.8247</v>
       </c>
     </row>
     <row r="15">
@@ -2121,7 +2121,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19">
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="21">
@@ -2464,22 +2464,22 @@
         <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M2" t="n">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="N2" t="n">
-        <v>581</v>
+        <v>587</v>
       </c>
       <c r="O2" t="n">
-        <v>894.4113</v>
+        <v>964.4529</v>
       </c>
       <c r="P2" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="Q2" t="n">
-        <v>28.852</v>
+        <v>27.5558</v>
       </c>
       <c r="R2" t="n">
         <v>215.2315</v>
@@ -2497,25 +2497,25 @@
         <v>0.5983000000000001</v>
       </c>
       <c r="W2" t="n">
-        <v>0.03881075</v>
+        <v>0.03987894</v>
       </c>
       <c r="X2" t="n">
-        <v>0.04576965</v>
+        <v>0.04624232</v>
       </c>
       <c r="Y2" t="n">
-        <v>3.2523</v>
+        <v>3.7169</v>
       </c>
       <c r="Z2" t="n">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="AA2" t="n">
-        <v>574</v>
+        <v>580</v>
       </c>
       <c r="AB2" t="n">
-        <v>251.066</v>
+        <v>259.1371</v>
       </c>
       <c r="AC2" t="n">
-        <v>663.7006</v>
+        <v>671.7716</v>
       </c>
       <c r="AD2" t="n">
         <v>6</v>
@@ -2527,7 +2527,7 @@
         <v>5</v>
       </c>
       <c r="AG2" t="n">
-        <v>7.8557</v>
+        <v>7.8052</v>
       </c>
     </row>
     <row r="3">
@@ -2565,22 +2565,22 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M3" t="n">
-        <v>194</v>
+        <v>210</v>
       </c>
       <c r="N3" t="n">
-        <v>502</v>
+        <v>518</v>
       </c>
       <c r="O3" t="n">
-        <v>825.0265000000001</v>
+        <v>843.2691</v>
       </c>
       <c r="P3" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="Q3" t="n">
-        <v>27.5009</v>
+        <v>25.5536</v>
       </c>
       <c r="R3" t="n">
         <v>126.468</v>
@@ -2598,28 +2598,28 @@
         <v>1</v>
       </c>
       <c r="W3" t="n">
-        <v>0.03115965</v>
+        <v>0.03372952</v>
       </c>
       <c r="X3" t="n">
-        <v>0.03393268</v>
+        <v>0.03501419</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.7443</v>
+        <v>3.9536</v>
       </c>
       <c r="Z3" t="n">
-        <v>157</v>
+        <v>196</v>
       </c>
       <c r="AA3" t="n">
-        <v>376</v>
+        <v>392</v>
       </c>
       <c r="AB3" t="n">
-        <v>224.1371</v>
+        <v>242.3797</v>
       </c>
       <c r="AC3" t="n">
-        <v>565.5168</v>
+        <v>583.7595</v>
       </c>
       <c r="AD3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE3" t="n">
         <v>8</v>
@@ -2628,7 +2628,7 @@
         <v>10</v>
       </c>
       <c r="AG3" t="n">
-        <v>7.7664</v>
+        <v>7.6954</v>
       </c>
     </row>
     <row r="4">
@@ -2666,22 +2666,22 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M4" t="n">
-        <v>368</v>
+        <v>390</v>
       </c>
       <c r="N4" t="n">
-        <v>687</v>
+        <v>709</v>
       </c>
       <c r="O4" t="n">
-        <v>1456.1535</v>
+        <v>1477.1535</v>
       </c>
       <c r="P4" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="Q4" t="n">
-        <v>27.4746</v>
+        <v>27.3547</v>
       </c>
       <c r="R4" t="n">
         <v>225.3087</v>
@@ -2699,28 +2699,28 @@
         <v>0.884</v>
       </c>
       <c r="W4" t="n">
-        <v>0.04391932</v>
+        <v>0.04654493</v>
       </c>
       <c r="X4" t="n">
-        <v>0.03554613</v>
+        <v>0.03668443</v>
       </c>
       <c r="Y4" t="n">
-        <v>5.7699</v>
+        <v>6.2137</v>
       </c>
       <c r="Z4" t="n">
-        <v>308</v>
+        <v>330</v>
       </c>
       <c r="AA4" t="n">
-        <v>632</v>
+        <v>654</v>
       </c>
       <c r="AB4" t="n">
-        <v>423.9899</v>
+        <v>445.5757</v>
       </c>
       <c r="AC4" t="n">
-        <v>782.2397</v>
+        <v>803.8255</v>
       </c>
       <c r="AD4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE4" t="n">
         <v>7</v>
@@ -2729,7 +2729,7 @@
         <v>10</v>
       </c>
       <c r="AG4" t="n">
-        <v>7.6771</v>
+        <v>7.5343</v>
       </c>
     </row>
     <row r="5">
@@ -2767,22 +2767,22 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="M5" t="n">
-        <v>255</v>
+        <v>286</v>
       </c>
       <c r="N5" t="n">
-        <v>657</v>
+        <v>688</v>
       </c>
       <c r="O5" t="n">
-        <v>344.5219</v>
+        <v>673.0436999999999</v>
       </c>
       <c r="P5" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="Q5" t="n">
-        <v>18.1327</v>
+        <v>24.9275</v>
       </c>
       <c r="R5" t="n">
         <v>151.7817</v>
@@ -2800,25 +2800,25 @@
         <v>1</v>
       </c>
       <c r="W5" t="n">
-        <v>0.03776659</v>
+        <v>0.04235782</v>
       </c>
       <c r="X5" t="n">
-        <v>0.04288232</v>
+        <v>0.04490569</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.9296</v>
+        <v>7.2472</v>
       </c>
       <c r="Z5" t="n">
-        <v>211</v>
+        <v>241</v>
       </c>
       <c r="AA5" t="n">
-        <v>338</v>
+        <v>368</v>
       </c>
       <c r="AB5" t="n">
-        <v>285.9655</v>
+        <v>319.0366</v>
       </c>
       <c r="AC5" t="n">
-        <v>736.2569</v>
+        <v>769.328</v>
       </c>
       <c r="AD5" t="n">
         <v>5</v>
@@ -2830,7 +2830,7 @@
         <v>8</v>
       </c>
       <c r="AG5" t="n">
-        <v>7.3342</v>
+        <v>6.8995</v>
       </c>
     </row>
     <row r="6">
@@ -2871,19 +2871,19 @@
         <v>10</v>
       </c>
       <c r="M6" t="n">
-        <v>380</v>
+        <v>413</v>
       </c>
       <c r="N6" t="n">
-        <v>1031</v>
+        <v>1064</v>
       </c>
       <c r="O6" t="n">
-        <v>2222.3099</v>
+        <v>2237.9667</v>
       </c>
       <c r="P6" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="Q6" t="n">
-        <v>22.9104</v>
+        <v>23.3122</v>
       </c>
       <c r="R6" t="n">
         <v>322.0427</v>
@@ -2901,28 +2901,28 @@
         <v>1</v>
       </c>
       <c r="W6" t="n">
-        <v>0.03258167</v>
+        <v>0.03541113</v>
       </c>
       <c r="X6" t="n">
-        <v>0.03594213</v>
+        <v>0.03709256</v>
       </c>
       <c r="Y6" t="n">
         <v>3.1052</v>
       </c>
       <c r="Z6" t="n">
-        <v>319</v>
+        <v>334</v>
       </c>
       <c r="AA6" t="n">
-        <v>837</v>
+        <v>859</v>
       </c>
       <c r="AB6" t="n">
-        <v>437.6468</v>
+        <v>475.7889</v>
       </c>
       <c r="AC6" t="n">
-        <v>1179.5311</v>
+        <v>1217.6732</v>
       </c>
       <c r="AD6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE6" t="n">
         <v>14</v>
@@ -2931,7 +2931,7 @@
         <v>13</v>
       </c>
       <c r="AG6" t="n">
-        <v>7.2803</v>
+        <v>7.2249</v>
       </c>
     </row>
     <row r="7">
@@ -2969,22 +2969,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M7" t="n">
-        <v>784</v>
+        <v>837</v>
       </c>
       <c r="N7" t="n">
-        <v>1661</v>
+        <v>1714</v>
       </c>
       <c r="O7" t="n">
-        <v>5469.8939</v>
+        <v>5172.1711</v>
       </c>
       <c r="P7" t="n">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="Q7" t="n">
-        <v>24.6392</v>
+        <v>23.6172</v>
       </c>
       <c r="R7" t="n">
         <v>438.5168</v>
@@ -3002,28 +3002,28 @@
         <v>1</v>
       </c>
       <c r="W7" t="n">
-        <v>0.05639882</v>
+        <v>0.0602115</v>
       </c>
       <c r="X7" t="n">
-        <v>0.05253669</v>
+        <v>0.05421306</v>
       </c>
       <c r="Y7" t="n">
-        <v>6.1571</v>
+        <v>6.3852</v>
       </c>
       <c r="Z7" t="n">
-        <v>781</v>
+        <v>834</v>
       </c>
       <c r="AA7" t="n">
-        <v>1566</v>
+        <v>1619</v>
       </c>
       <c r="AB7" t="n">
-        <v>902.4651</v>
+        <v>964.9209</v>
       </c>
       <c r="AC7" t="n">
-        <v>1908.8297</v>
+        <v>1971.2855</v>
       </c>
       <c r="AD7" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AE7" t="n">
         <v>20</v>
@@ -3032,7 +3032,7 @@
         <v>22</v>
       </c>
       <c r="AG7" t="n">
-        <v>7.6259</v>
+        <v>7.5889</v>
       </c>
     </row>
     <row r="8">
@@ -3073,19 +3073,19 @@
         <v>16</v>
       </c>
       <c r="M8" t="n">
-        <v>410</v>
+        <v>423</v>
       </c>
       <c r="N8" t="n">
-        <v>749</v>
+        <v>762</v>
       </c>
       <c r="O8" t="n">
-        <v>822.1981</v>
+        <v>832.7838</v>
       </c>
       <c r="P8" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="Q8" t="n">
-        <v>22.8388</v>
+        <v>21.9154</v>
       </c>
       <c r="R8" t="n">
         <v>211.9239</v>
@@ -3103,25 +3103,25 @@
         <v>1</v>
       </c>
       <c r="W8" t="n">
-        <v>0.04867624</v>
+        <v>0.05021964</v>
       </c>
       <c r="X8" t="n">
-        <v>0.03974318</v>
+        <v>0.04043298</v>
       </c>
       <c r="Y8" t="n">
         <v>7.5499</v>
       </c>
       <c r="Z8" t="n">
-        <v>351</v>
+        <v>364</v>
       </c>
       <c r="AA8" t="n">
-        <v>547</v>
+        <v>560</v>
       </c>
       <c r="AB8" t="n">
-        <v>464.262</v>
+        <v>477.6762</v>
       </c>
       <c r="AC8" t="n">
-        <v>849.5118</v>
+        <v>862.926</v>
       </c>
       <c r="AD8" t="n">
         <v>8</v>
@@ -3133,7 +3133,7 @@
         <v>11</v>
       </c>
       <c r="AG8" t="n">
-        <v>7.4551</v>
+        <v>7.3911</v>
       </c>
     </row>
     <row r="9">
@@ -3171,22 +3171,22 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M9" t="n">
-        <v>459</v>
+        <v>482</v>
       </c>
       <c r="N9" t="n">
-        <v>883</v>
+        <v>906</v>
       </c>
       <c r="O9" t="n">
-        <v>919.9675999999999</v>
+        <v>966.0092</v>
       </c>
       <c r="P9" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="Q9" t="n">
-        <v>20.9084</v>
+        <v>20.5534</v>
       </c>
       <c r="R9" t="n">
         <v>359.1909</v>
@@ -3204,28 +3204,28 @@
         <v>0.9025</v>
       </c>
       <c r="W9" t="n">
-        <v>0.03706695</v>
+        <v>0.03892433</v>
       </c>
       <c r="X9" t="n">
-        <v>0.03275101</v>
+        <v>0.03360409</v>
       </c>
       <c r="Y9" t="n">
-        <v>4.7329</v>
+        <v>4.4545</v>
       </c>
       <c r="Z9" t="n">
-        <v>415</v>
+        <v>453</v>
       </c>
       <c r="AA9" t="n">
-        <v>691</v>
+        <v>731</v>
       </c>
       <c r="AB9" t="n">
-        <v>514.3036</v>
+        <v>543.4457</v>
       </c>
       <c r="AC9" t="n">
-        <v>987.4234</v>
+        <v>1016.1514</v>
       </c>
       <c r="AD9" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AE9" t="n">
         <v>11</v>
@@ -3234,7 +3234,7 @@
         <v>10</v>
       </c>
       <c r="AG9" t="n">
-        <v>7.5163</v>
+        <v>7.6519</v>
       </c>
     </row>
     <row r="10">
@@ -3272,22 +3272,22 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M10" t="n">
-        <v>388</v>
+        <v>406</v>
       </c>
       <c r="N10" t="n">
-        <v>960</v>
+        <v>981</v>
       </c>
       <c r="O10" t="n">
-        <v>2091.6286</v>
+        <v>2042.0723</v>
       </c>
       <c r="P10" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="Q10" t="n">
-        <v>22.7351</v>
+        <v>21.7242</v>
       </c>
       <c r="R10" t="n">
         <v>302.4508</v>
@@ -3305,25 +3305,25 @@
         <v>1</v>
       </c>
       <c r="W10" t="n">
-        <v>0.03546618</v>
+        <v>0.03711152</v>
       </c>
       <c r="X10" t="n">
-        <v>0.03874874</v>
+        <v>0.03959637</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.3144</v>
+        <v>2.6451</v>
       </c>
       <c r="Z10" t="n">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="AA10" t="n">
-        <v>537</v>
+        <v>550</v>
       </c>
       <c r="AB10" t="n">
-        <v>436.0904</v>
+        <v>456.7473</v>
       </c>
       <c r="AC10" t="n">
-        <v>1075.2641</v>
+        <v>1098.9209</v>
       </c>
       <c r="AD10" t="n">
         <v>11</v>
@@ -3335,7 +3335,7 @@
         <v>12</v>
       </c>
       <c r="AG10" t="n">
-        <v>8.643700000000001</v>
+        <v>8.543200000000001</v>
       </c>
     </row>
     <row r="11">
@@ -3373,22 +3373,22 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="M11" t="n">
-        <v>465</v>
+        <v>512</v>
       </c>
       <c r="N11" t="n">
-        <v>1270</v>
+        <v>1310</v>
       </c>
       <c r="O11" t="n">
-        <v>3280.2775</v>
+        <v>4028.4167</v>
       </c>
       <c r="P11" t="n">
-        <v>134</v>
+        <v>162</v>
       </c>
       <c r="Q11" t="n">
-        <v>24.4797</v>
+        <v>24.8668</v>
       </c>
       <c r="R11" t="n">
         <v>309.5219</v>
@@ -3406,37 +3406,37 @@
         <v>1</v>
       </c>
       <c r="W11" t="n">
-        <v>0.04101614</v>
+        <v>0.04516186</v>
       </c>
       <c r="X11" t="n">
-        <v>0.04489854</v>
+        <v>0.04631266</v>
       </c>
       <c r="Y11" t="n">
-        <v>5.4923</v>
+        <v>4.8462</v>
       </c>
       <c r="Z11" t="n">
-        <v>444</v>
+        <v>501</v>
       </c>
       <c r="AA11" t="n">
-        <v>1094</v>
+        <v>1290</v>
       </c>
       <c r="AB11" t="n">
-        <v>534.5168</v>
+        <v>589.1442</v>
       </c>
       <c r="AC11" t="n">
-        <v>1452.8692</v>
+        <v>1504.9819</v>
       </c>
       <c r="AD11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AE11" t="n">
         <v>14</v>
       </c>
       <c r="AF11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AG11" t="n">
-        <v>7.7735</v>
+        <v>7.6136</v>
       </c>
     </row>
     <row r="12">
@@ -3477,19 +3477,19 @@
         <v>20</v>
       </c>
       <c r="M12" t="n">
-        <v>767</v>
+        <v>815</v>
       </c>
       <c r="N12" t="n">
-        <v>1786</v>
+        <v>1834</v>
       </c>
       <c r="O12" t="n">
-        <v>4088.0908</v>
+        <v>4102.7476</v>
       </c>
       <c r="P12" t="n">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="Q12" t="n">
-        <v>19.0144</v>
+        <v>18.6489</v>
       </c>
       <c r="R12" t="n">
         <v>468.2742</v>
@@ -3507,28 +3507,28 @@
         <v>1</v>
       </c>
       <c r="W12" t="n">
-        <v>0.04992514</v>
+        <v>0.05304953</v>
       </c>
       <c r="X12" t="n">
-        <v>0.05238151</v>
+        <v>0.0537893</v>
       </c>
       <c r="Y12" t="n">
         <v>4.271</v>
       </c>
       <c r="Z12" t="n">
-        <v>686</v>
+        <v>715</v>
       </c>
       <c r="AA12" t="n">
-        <v>1687</v>
+        <v>1723</v>
       </c>
       <c r="AB12" t="n">
-        <v>873.6539</v>
+        <v>930.6955</v>
       </c>
       <c r="AC12" t="n">
-        <v>2015.19</v>
+        <v>2072.2317</v>
       </c>
       <c r="AD12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AE12" t="n">
         <v>22</v>
@@ -3537,7 +3537,7 @@
         <v>25</v>
       </c>
       <c r="AG12" t="n">
-        <v>7.4169</v>
+        <v>7.3385</v>
       </c>
     </row>
     <row r="13">
@@ -3575,22 +3575,22 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="M13" t="n">
-        <v>601</v>
+        <v>652</v>
       </c>
       <c r="N13" t="n">
-        <v>1342</v>
+        <v>1393</v>
       </c>
       <c r="O13" t="n">
-        <v>2217.9007</v>
+        <v>2361.1556</v>
       </c>
       <c r="P13" t="n">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="Q13" t="n">
-        <v>20.9236</v>
+        <v>20.5318</v>
       </c>
       <c r="R13" t="n">
         <v>422.9777</v>
@@ -3608,28 +3608,28 @@
         <v>1</v>
       </c>
       <c r="W13" t="n">
-        <v>0.04565135</v>
+        <v>0.04952526</v>
       </c>
       <c r="X13" t="n">
-        <v>0.04473184</v>
+        <v>0.04643179</v>
       </c>
       <c r="Y13" t="n">
-        <v>4.492</v>
+        <v>5.2012</v>
       </c>
       <c r="Z13" t="n">
-        <v>530</v>
+        <v>610</v>
       </c>
       <c r="AA13" t="n">
-        <v>1121</v>
+        <v>1227</v>
       </c>
       <c r="AB13" t="n">
-        <v>674.2864</v>
+        <v>732.2569</v>
       </c>
       <c r="AC13" t="n">
-        <v>1515.7981</v>
+        <v>1573.7687</v>
       </c>
       <c r="AD13" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AE13" t="n">
         <v>16</v>
@@ -3638,7 +3638,7 @@
         <v>15</v>
       </c>
       <c r="AG13" t="n">
-        <v>7.1869</v>
+        <v>7.0766</v>
       </c>
     </row>
     <row r="14">
@@ -3676,22 +3676,22 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="M14" t="n">
-        <v>608</v>
+        <v>636</v>
       </c>
       <c r="N14" t="n">
-        <v>1318</v>
+        <v>1349</v>
       </c>
       <c r="O14" t="n">
-        <v>2788.4297</v>
+        <v>2398.6825</v>
       </c>
       <c r="P14" t="n">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="Q14" t="n">
-        <v>20.5032</v>
+        <v>18.8873</v>
       </c>
       <c r="R14" t="n">
         <v>379.8478</v>
@@ -3709,28 +3709,28 @@
         <v>1</v>
       </c>
       <c r="W14" t="n">
-        <v>0.04572804</v>
+        <v>0.04783394</v>
       </c>
       <c r="X14" t="n">
-        <v>0.04104896</v>
+        <v>0.04201445</v>
       </c>
       <c r="Y14" t="n">
-        <v>5.2653</v>
+        <v>6.0551</v>
       </c>
       <c r="Z14" t="n">
-        <v>570</v>
+        <v>611</v>
       </c>
       <c r="AA14" t="n">
-        <v>1215</v>
+        <v>1259</v>
       </c>
       <c r="AB14" t="n">
-        <v>688.6711</v>
+        <v>720.5706</v>
       </c>
       <c r="AC14" t="n">
-        <v>1491.8692</v>
+        <v>1527.1829</v>
       </c>
       <c r="AD14" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AE14" t="n">
         <v>22</v>
@@ -3739,7 +3739,7 @@
         <v>19</v>
       </c>
       <c r="AG14" t="n">
-        <v>7.6692</v>
+        <v>7.7579</v>
       </c>
     </row>
     <row r="15">
@@ -3777,22 +3777,22 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M15" t="n">
-        <v>318</v>
+        <v>300</v>
       </c>
       <c r="N15" t="n">
-        <v>855</v>
+        <v>702</v>
       </c>
       <c r="O15" t="n">
-        <v>2153.653</v>
+        <v>2268.7657</v>
       </c>
       <c r="P15" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="Q15" t="n">
-        <v>28.7154</v>
+        <v>26.6914</v>
       </c>
       <c r="R15" t="n">
         <v>217.9239</v>
@@ -3810,37 +3810,37 @@
         <v>1</v>
       </c>
       <c r="W15" t="n">
-        <v>0.03601359</v>
+        <v>0.03397508</v>
       </c>
       <c r="X15" t="n">
-        <v>0.03719655</v>
+        <v>0.03054033</v>
       </c>
       <c r="Y15" t="n">
-        <v>4.1299</v>
+        <v>4.5888</v>
       </c>
       <c r="Z15" t="n">
-        <v>227</v>
+        <v>259</v>
       </c>
       <c r="AA15" t="n">
-        <v>546</v>
+        <v>579</v>
       </c>
       <c r="AB15" t="n">
-        <v>358.9066</v>
+        <v>334.0366</v>
       </c>
       <c r="AC15" t="n">
-        <v>969.4945</v>
+        <v>789.2275</v>
       </c>
       <c r="AD15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE15" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AF15" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AG15" t="n">
-        <v>6.6409</v>
+        <v>6.5975</v>
       </c>
     </row>
     <row r="16">
@@ -3878,22 +3878,22 @@
         <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M16" t="n">
-        <v>274</v>
+        <v>372</v>
       </c>
       <c r="N16" t="n">
-        <v>679</v>
+        <v>904</v>
       </c>
       <c r="O16" t="n">
-        <v>862.997</v>
+        <v>2422.0256</v>
       </c>
       <c r="P16" t="n">
-        <v>44</v>
+        <v>92</v>
       </c>
       <c r="Q16" t="n">
-        <v>19.6136</v>
+        <v>26.3264</v>
       </c>
       <c r="R16" t="n">
         <v>332.8944</v>
@@ -3911,37 +3911,37 @@
         <v>0.7919</v>
       </c>
       <c r="W16" t="n">
-        <v>0.02608282</v>
+        <v>0.03541171</v>
       </c>
       <c r="X16" t="n">
-        <v>0.02852222</v>
+        <v>0.03797362</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.8024</v>
+        <v>2.4032</v>
       </c>
       <c r="Z16" t="n">
-        <v>187</v>
+        <v>310</v>
       </c>
       <c r="AA16" t="n">
-        <v>280</v>
+        <v>705</v>
       </c>
       <c r="AB16" t="n">
-        <v>305.5219</v>
+        <v>418.6051</v>
       </c>
       <c r="AC16" t="n">
-        <v>756.8133</v>
+        <v>1017.394</v>
       </c>
       <c r="AD16" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AE16" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AF16" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AG16" t="n">
-        <v>7.6559</v>
+        <v>7.5598</v>
       </c>
     </row>
     <row r="17">
@@ -3979,22 +3979,22 @@
         <v>1</v>
       </c>
       <c r="L17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M17" t="n">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="N17" t="n">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="O17" t="n">
-        <v>95.4264</v>
+        <v>65.4558</v>
       </c>
       <c r="P17" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q17" t="n">
-        <v>13.6323</v>
+        <v>10.9093</v>
       </c>
       <c r="R17" t="n">
         <v>205.7756</v>
@@ -4012,25 +4012,25 @@
         <v>0.714</v>
       </c>
       <c r="W17" t="n">
-        <v>0.02187408</v>
+        <v>0.02276086</v>
       </c>
       <c r="X17" t="n">
-        <v>0.03050682</v>
+        <v>0.03087363</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.4298</v>
+        <v>1.9439</v>
       </c>
       <c r="Z17" t="n">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="AA17" t="n">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="AB17" t="n">
-        <v>164.3675</v>
+        <v>170.9533</v>
       </c>
       <c r="AC17" t="n">
-        <v>551.9605</v>
+        <v>558.5462</v>
       </c>
       <c r="AD17" t="n">
         <v>4</v>
@@ -4042,7 +4042,7 @@
         <v>6</v>
       </c>
       <c r="AG17" t="n">
-        <v>5.8635</v>
+        <v>5.3984</v>
       </c>
     </row>
     <row r="18">
@@ -4059,22 +4059,22 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M18" t="n">
-        <v>564</v>
+        <v>582</v>
       </c>
       <c r="N18" t="n">
-        <v>1304</v>
+        <v>1325</v>
       </c>
       <c r="O18" t="n">
-        <v>1184.2885</v>
+        <v>1512.6804</v>
       </c>
       <c r="P18" t="n">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="Q18" t="n">
-        <v>20.4188</v>
+        <v>21.9229</v>
       </c>
       <c r="R18" t="n">
         <v>387.9483</v>
@@ -4092,28 +4092,28 @@
         <v>1</v>
       </c>
       <c r="W18" t="n">
-        <v>0.04326149</v>
+        <v>0.04464217</v>
       </c>
       <c r="X18" t="n">
-        <v>0.04190231</v>
+        <v>0.04257712</v>
       </c>
       <c r="Y18" t="n">
-        <v>4.382</v>
+        <v>4.1243</v>
       </c>
       <c r="Z18" t="n">
-        <v>485</v>
+        <v>503</v>
       </c>
       <c r="AA18" t="n">
-        <v>842</v>
+        <v>859</v>
       </c>
       <c r="AB18" t="n">
-        <v>650.1564</v>
+        <v>672.4701</v>
       </c>
       <c r="AC18" t="n">
-        <v>1509.5921</v>
+        <v>1535.9058</v>
       </c>
       <c r="AD18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AE18" t="n">
         <v>16</v>
@@ -4122,7 +4122,7 @@
         <v>18</v>
       </c>
       <c r="AG18" t="n">
-        <v>7.6596</v>
+        <v>7.6131</v>
       </c>
     </row>
     <row r="19">
@@ -4142,19 +4142,19 @@
         <v>2</v>
       </c>
       <c r="M19" t="n">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="N19" t="n">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="O19" t="n">
-        <v>389.9483</v>
+        <v>399.1909</v>
       </c>
       <c r="P19" t="n">
         <v>18</v>
       </c>
       <c r="Q19" t="n">
-        <v>21.6638</v>
+        <v>22.1773</v>
       </c>
       <c r="R19" t="n">
         <v>87.0061</v>
@@ -4172,28 +4172,28 @@
         <v>0.5282</v>
       </c>
       <c r="W19" t="n">
-        <v>0.02367067</v>
+        <v>0.02641509</v>
       </c>
       <c r="X19" t="n">
-        <v>0.02184214</v>
+        <v>0.02276667</v>
       </c>
       <c r="Y19" t="n">
         <v>2.2987</v>
       </c>
       <c r="Z19" t="n">
-        <v>36</v>
+        <v>61</v>
       </c>
       <c r="AA19" t="n">
-        <v>97</v>
+        <v>156</v>
       </c>
       <c r="AB19" t="n">
-        <v>79.7696</v>
+        <v>89.01220000000001</v>
       </c>
       <c r="AC19" t="n">
-        <v>213.267</v>
+        <v>222.5097</v>
       </c>
       <c r="AD19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE19" t="n">
         <v>3</v>
@@ -4202,7 +4202,7 @@
         <v>4</v>
       </c>
       <c r="AG19" t="n">
-        <v>8.4397</v>
+        <v>8.425000000000001</v>
       </c>
     </row>
     <row r="20">

--- a/results/542_z06/5_quantification/542_z06_quantification.xlsx
+++ b/results/542_z06/5_quantification/542_z06_quantification.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -699,13 +699,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>14.5333</v>
+        <v>15.1333</v>
       </c>
       <c r="D12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E12" t="n">
-        <v>6.7809</v>
+        <v>6.8958</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -728,13 +728,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>473.2</v>
+        <v>485.5333</v>
       </c>
       <c r="D13" t="n">
-        <v>423</v>
+        <v>459</v>
       </c>
       <c r="E13" t="n">
-        <v>202.6359</v>
+        <v>197.3586</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -757,13 +757,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1032.7333</v>
+        <v>1045.7333</v>
       </c>
       <c r="D14" t="n">
-        <v>981</v>
+        <v>992</v>
       </c>
       <c r="E14" t="n">
-        <v>449.1294</v>
+        <v>448.8365</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -786,13 +786,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2075.1267</v>
+        <v>2175.8237</v>
       </c>
       <c r="D15" t="n">
-        <v>2042.0723</v>
+        <v>2113.8713</v>
       </c>
       <c r="E15" t="n">
-        <v>1418.7375</v>
+        <v>1373.0877</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -815,13 +815,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>93.33329999999999</v>
+        <v>99.9333</v>
       </c>
       <c r="D16" t="n">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="E16" t="n">
-        <v>65.4181</v>
+        <v>64.7373</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -844,13 +844,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>22.3671</v>
+        <v>21.7572</v>
       </c>
       <c r="D17" t="n">
-        <v>21.9229</v>
+        <v>21.6373</v>
       </c>
       <c r="E17" t="n">
-        <v>3.3454</v>
+        <v>3.0691</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1018,13 +1018,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.04403868</v>
+        <v>0.04568601</v>
       </c>
       <c r="D23" t="n">
-        <v>0.04464217</v>
+        <v>0.04568942</v>
       </c>
       <c r="E23" t="n">
-        <v>0.00754502</v>
+        <v>0.00665998</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1047,13 +1047,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.04109938</v>
+        <v>0.04182451</v>
       </c>
       <c r="D24" t="n">
-        <v>0.04043298</v>
+        <v>0.04032686</v>
       </c>
       <c r="E24" t="n">
-        <v>0.00712237</v>
+        <v>0.00704682</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1076,13 +1076,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>5.1783</v>
+        <v>5.546</v>
       </c>
       <c r="D25" t="n">
-        <v>4.8462</v>
+        <v>5.2653</v>
       </c>
       <c r="E25" t="n">
-        <v>1.5065</v>
+        <v>1.7789</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1105,13 +1105,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>424.8667</v>
+        <v>445.2667</v>
       </c>
       <c r="D26" t="n">
-        <v>364</v>
+        <v>404</v>
       </c>
       <c r="E26" t="n">
-        <v>203.6341</v>
+        <v>197.6044</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1134,13 +1134,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>852.9333</v>
+        <v>892.7333</v>
       </c>
       <c r="D27" t="n">
-        <v>731</v>
+        <v>690</v>
       </c>
       <c r="E27" t="n">
-        <v>472.5172</v>
+        <v>461.0799</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1163,13 +1163,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>538.1704</v>
+        <v>552.5835</v>
       </c>
       <c r="D28" t="n">
-        <v>477.6762</v>
+        <v>514.7178</v>
       </c>
       <c r="E28" t="n">
-        <v>233.7423</v>
+        <v>228.6159</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1192,13 +1192,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1172.3557</v>
+        <v>1187.5687</v>
       </c>
       <c r="D29" t="n">
-        <v>1098.9209</v>
+        <v>1109.9209</v>
       </c>
       <c r="E29" t="n">
-        <v>516.3555</v>
+        <v>515.9711</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1224,10 +1224,10 @@
         <v>10.7333</v>
       </c>
       <c r="D30" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E30" t="n">
-        <v>5.7998</v>
+        <v>5.2026</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1250,13 +1250,13 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>13.1333</v>
+        <v>13.2667</v>
       </c>
       <c r="D31" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E31" t="n">
-        <v>5.4362</v>
+        <v>5.3381</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1279,13 +1279,13 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>13.6</v>
+        <v>13.6667</v>
       </c>
       <c r="D32" t="n">
         <v>12</v>
       </c>
       <c r="E32" t="n">
-        <v>5.4485</v>
+        <v>5.5119</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1299,29 +1299,87 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>loop_count</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>loops, report only</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="D33" t="n">
+        <v>5</v>
+      </c>
+      <c r="E33" t="n">
+        <v>8.019600000000001</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>loop_edge_share</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>loops, report only</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>0.2613</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.2283</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.1204</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>share</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>ring_width_mean_r30_px</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>width</t>
         </is>
       </c>
-      <c r="C33" t="n">
-        <v>7.4697</v>
-      </c>
-      <c r="D33" t="n">
-        <v>7.5343</v>
-      </c>
-      <c r="E33" t="n">
-        <v>0.4396</v>
-      </c>
-      <c r="F33" t="inlineStr">
+      <c r="C35" t="n">
+        <v>7.6454</v>
+      </c>
+      <c r="D35" t="n">
+        <v>7.62</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.4946</v>
+      </c>
+      <c r="F35" t="inlineStr">
         <is>
           <t>px</t>
         </is>
       </c>
-      <c r="G33" t="n">
+      <c r="G35" t="n">
         <v>15</v>
       </c>
     </row>
@@ -1336,7 +1394,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1393,7 +1451,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>39890</v>
+        <v>40198</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1413,7 +1471,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.03963621</v>
+        <v>0.03994225</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1433,7 +1491,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>905</v>
+        <v>934</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1453,7 +1511,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.00089924</v>
+        <v>0.00092806</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1513,7 +1571,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1533,7 +1591,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>169.7447</v>
+        <v>177.0837</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1553,7 +1611,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1573,7 +1631,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.0448956</v>
+        <v>0.04524032</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1593,7 +1651,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.03960452</v>
+        <v>0.03982589</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1630,7 +1688,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>375</v>
+        <v>355</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1650,7 +1708,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1670,7 +1728,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.03963621</v>
+        <v>0.03994225</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1690,11 +1748,71 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.04000882</v>
+        <v>0.04029499</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
           <t>px^-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>loop_count</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>159</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>loop_edge_share</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>0.3259</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>share</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>edge_count</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>2007</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>count</t>
         </is>
       </c>
     </row>
@@ -1746,7 +1864,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8.1721</v>
+        <v>8.2188</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1786,7 +1904,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4.4721</v>
+        <v>5.6569</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1826,7 +1944,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>38643</v>
+        <v>38859</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1969,7 +2087,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>770</v>
+        <v>775</v>
       </c>
     </row>
     <row r="9">
@@ -1984,7 +2102,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>13.5754</v>
+        <v>13.3116</v>
       </c>
     </row>
     <row r="10">
@@ -2014,7 +2132,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>32.7814</v>
+        <v>32.0544</v>
       </c>
     </row>
     <row r="12">
@@ -2044,7 +2162,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.1753</v>
+        <v>0.1742</v>
       </c>
     </row>
     <row r="14">
@@ -2059,7 +2177,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.8247</v>
+        <v>0.8258</v>
       </c>
     </row>
     <row r="15">
@@ -2121,7 +2239,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19">
@@ -2136,7 +2254,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -2151,7 +2269,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="21">
@@ -2230,7 +2348,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.5814</v>
+        <v>0.7354000000000001</v>
       </c>
     </row>
     <row r="26">
@@ -2259,7 +2377,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG20"/>
+  <dimension ref="A1:AI20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2428,6 +2546,16 @@
           <t>ring_width_mean_r30_px</t>
         </is>
       </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>loop_count</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>loop_edge_share</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -2464,22 +2592,22 @@
         <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M2" t="n">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="N2" t="n">
         <v>587</v>
       </c>
       <c r="O2" t="n">
-        <v>964.4529</v>
+        <v>843.2691</v>
       </c>
       <c r="P2" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="Q2" t="n">
-        <v>27.5558</v>
+        <v>24.802</v>
       </c>
       <c r="R2" t="n">
         <v>215.2315</v>
@@ -2497,25 +2625,25 @@
         <v>0.5983000000000001</v>
       </c>
       <c r="W2" t="n">
-        <v>0.03987894</v>
+        <v>0.03881075</v>
       </c>
       <c r="X2" t="n">
         <v>0.04624232</v>
       </c>
       <c r="Y2" t="n">
-        <v>3.7169</v>
+        <v>3.2523</v>
       </c>
       <c r="Z2" t="n">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="AA2" t="n">
         <v>580</v>
       </c>
       <c r="AB2" t="n">
-        <v>259.1371</v>
+        <v>251.4802</v>
       </c>
       <c r="AC2" t="n">
-        <v>671.7716</v>
+        <v>670.1147999999999</v>
       </c>
       <c r="AD2" t="n">
         <v>6</v>
@@ -2527,7 +2655,13 @@
         <v>5</v>
       </c>
       <c r="AG2" t="n">
-        <v>7.8052</v>
+        <v>7.8744</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -2565,22 +2699,22 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="M3" t="n">
-        <v>210</v>
+        <v>278</v>
       </c>
       <c r="N3" t="n">
-        <v>518</v>
+        <v>584</v>
       </c>
       <c r="O3" t="n">
-        <v>843.2691</v>
+        <v>906.5828</v>
       </c>
       <c r="P3" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="Q3" t="n">
-        <v>25.5536</v>
+        <v>22.6646</v>
       </c>
       <c r="R3" t="n">
         <v>126.468</v>
@@ -2598,25 +2732,25 @@
         <v>1</v>
       </c>
       <c r="W3" t="n">
-        <v>0.03372952</v>
+        <v>0.04465146</v>
       </c>
       <c r="X3" t="n">
-        <v>0.03501419</v>
+        <v>0.03947546</v>
       </c>
       <c r="Y3" t="n">
-        <v>3.9536</v>
+        <v>6.3257</v>
       </c>
       <c r="Z3" t="n">
-        <v>196</v>
+        <v>259</v>
       </c>
       <c r="AA3" t="n">
-        <v>392</v>
+        <v>453</v>
       </c>
       <c r="AB3" t="n">
-        <v>242.3797</v>
+        <v>316.1787</v>
       </c>
       <c r="AC3" t="n">
-        <v>583.7595</v>
+        <v>657.9727</v>
       </c>
       <c r="AD3" t="n">
         <v>5</v>
@@ -2625,10 +2759,16 @@
         <v>8</v>
       </c>
       <c r="AF3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AG3" t="n">
-        <v>7.6954</v>
+        <v>8.654999999999999</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.15</v>
       </c>
     </row>
     <row r="4">
@@ -2669,19 +2809,19 @@
         <v>14</v>
       </c>
       <c r="M4" t="n">
-        <v>390</v>
+        <v>376</v>
       </c>
       <c r="N4" t="n">
-        <v>709</v>
+        <v>696</v>
       </c>
       <c r="O4" t="n">
-        <v>1477.1535</v>
+        <v>1457.7392</v>
       </c>
       <c r="P4" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="Q4" t="n">
-        <v>27.3547</v>
+        <v>27.5045</v>
       </c>
       <c r="R4" t="n">
         <v>225.3087</v>
@@ -2699,25 +2839,25 @@
         <v>0.884</v>
       </c>
       <c r="W4" t="n">
-        <v>0.04654493</v>
+        <v>0.04487409</v>
       </c>
       <c r="X4" t="n">
-        <v>0.03668443</v>
+        <v>0.0360118</v>
       </c>
       <c r="Y4" t="n">
         <v>6.2137</v>
       </c>
       <c r="Z4" t="n">
-        <v>330</v>
+        <v>316</v>
       </c>
       <c r="AA4" t="n">
-        <v>654</v>
+        <v>641</v>
       </c>
       <c r="AB4" t="n">
-        <v>445.5757</v>
+        <v>432.4041</v>
       </c>
       <c r="AC4" t="n">
-        <v>803.8255</v>
+        <v>791.6539</v>
       </c>
       <c r="AD4" t="n">
         <v>8</v>
@@ -2729,7 +2869,13 @@
         <v>10</v>
       </c>
       <c r="AG4" t="n">
-        <v>7.5343</v>
+        <v>7.6517</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.1321</v>
       </c>
     </row>
     <row r="5">
@@ -2767,22 +2913,22 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M5" t="n">
-        <v>286</v>
+        <v>317</v>
       </c>
       <c r="N5" t="n">
-        <v>688</v>
+        <v>716</v>
       </c>
       <c r="O5" t="n">
-        <v>673.0436999999999</v>
+        <v>1201.8032</v>
       </c>
       <c r="P5" t="n">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="Q5" t="n">
-        <v>24.9275</v>
+        <v>23.1116</v>
       </c>
       <c r="R5" t="n">
         <v>151.7817</v>
@@ -2800,37 +2946,43 @@
         <v>1</v>
       </c>
       <c r="W5" t="n">
-        <v>0.04235782</v>
+        <v>0.04694905</v>
       </c>
       <c r="X5" t="n">
-        <v>0.04490569</v>
+        <v>0.04673324</v>
       </c>
       <c r="Y5" t="n">
-        <v>7.2472</v>
+        <v>7.9061</v>
       </c>
       <c r="Z5" t="n">
-        <v>241</v>
+        <v>313</v>
       </c>
       <c r="AA5" t="n">
-        <v>368</v>
+        <v>607</v>
       </c>
       <c r="AB5" t="n">
-        <v>319.0366</v>
+        <v>356.1787</v>
       </c>
       <c r="AC5" t="n">
-        <v>769.328</v>
+        <v>803.0559</v>
       </c>
       <c r="AD5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE5" t="n">
         <v>7</v>
       </c>
       <c r="AF5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG5" t="n">
-        <v>6.8995</v>
+        <v>7.0968</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0.1731</v>
       </c>
     </row>
     <row r="6">
@@ -2871,19 +3023,19 @@
         <v>10</v>
       </c>
       <c r="M6" t="n">
-        <v>413</v>
+        <v>462</v>
       </c>
       <c r="N6" t="n">
-        <v>1064</v>
+        <v>1118</v>
       </c>
       <c r="O6" t="n">
-        <v>2237.9667</v>
+        <v>3418.6988</v>
       </c>
       <c r="P6" t="n">
-        <v>96</v>
+        <v>158</v>
       </c>
       <c r="Q6" t="n">
-        <v>23.3122</v>
+        <v>21.6373</v>
       </c>
       <c r="R6" t="n">
         <v>322.0427</v>
@@ -2901,37 +3053,43 @@
         <v>1</v>
       </c>
       <c r="W6" t="n">
-        <v>0.03541113</v>
+        <v>0.03961245</v>
       </c>
       <c r="X6" t="n">
-        <v>0.03709256</v>
+        <v>0.03897507</v>
       </c>
       <c r="Y6" t="n">
         <v>3.1052</v>
       </c>
       <c r="Z6" t="n">
-        <v>334</v>
+        <v>404</v>
       </c>
       <c r="AA6" t="n">
-        <v>859</v>
+        <v>958</v>
       </c>
       <c r="AB6" t="n">
-        <v>475.7889</v>
+        <v>537.3158</v>
       </c>
       <c r="AC6" t="n">
-        <v>1217.6732</v>
+        <v>1286.857</v>
       </c>
       <c r="AD6" t="n">
         <v>9</v>
       </c>
       <c r="AE6" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AF6" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>7.7589</v>
+      </c>
+      <c r="AH6" t="n">
         <v>13</v>
       </c>
-      <c r="AG6" t="n">
-        <v>7.2249</v>
+      <c r="AI6" t="n">
+        <v>0.3291</v>
       </c>
     </row>
     <row r="7">
@@ -2969,22 +3127,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M7" t="n">
-        <v>837</v>
+        <v>830</v>
       </c>
       <c r="N7" t="n">
-        <v>1714</v>
+        <v>1707</v>
       </c>
       <c r="O7" t="n">
-        <v>5172.1711</v>
+        <v>4818.1517</v>
       </c>
       <c r="P7" t="n">
-        <v>219</v>
+        <v>205</v>
       </c>
       <c r="Q7" t="n">
-        <v>23.6172</v>
+        <v>23.5032</v>
       </c>
       <c r="R7" t="n">
         <v>438.5168</v>
@@ -3002,28 +3160,28 @@
         <v>1</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0602115</v>
+        <v>0.05970793</v>
       </c>
       <c r="X7" t="n">
-        <v>0.05421306</v>
+        <v>0.05399165</v>
       </c>
       <c r="Y7" t="n">
-        <v>6.3852</v>
+        <v>6.6132</v>
       </c>
       <c r="Z7" t="n">
-        <v>834</v>
+        <v>827</v>
       </c>
       <c r="AA7" t="n">
-        <v>1619</v>
+        <v>1612</v>
       </c>
       <c r="AB7" t="n">
-        <v>964.9209</v>
+        <v>956.2641</v>
       </c>
       <c r="AC7" t="n">
-        <v>1971.2855</v>
+        <v>1962.6286</v>
       </c>
       <c r="AD7" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AE7" t="n">
         <v>20</v>
@@ -3032,7 +3190,13 @@
         <v>22</v>
       </c>
       <c r="AG7" t="n">
-        <v>7.5889</v>
+        <v>7.6195</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0.4341</v>
       </c>
     </row>
     <row r="8">
@@ -3073,19 +3237,19 @@
         <v>16</v>
       </c>
       <c r="M8" t="n">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="N8" t="n">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="O8" t="n">
-        <v>832.7838</v>
+        <v>890.0681</v>
       </c>
       <c r="P8" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="Q8" t="n">
-        <v>21.9154</v>
+        <v>22.2517</v>
       </c>
       <c r="R8" t="n">
         <v>211.9239</v>
@@ -3103,37 +3267,43 @@
         <v>1</v>
       </c>
       <c r="W8" t="n">
-        <v>0.05021964</v>
+        <v>0.04998219</v>
       </c>
       <c r="X8" t="n">
-        <v>0.04043298</v>
+        <v>0.04032686</v>
       </c>
       <c r="Y8" t="n">
         <v>7.5499</v>
       </c>
       <c r="Z8" t="n">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="AA8" t="n">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="AB8" t="n">
-        <v>477.6762</v>
+        <v>474.4335</v>
       </c>
       <c r="AC8" t="n">
-        <v>862.926</v>
+        <v>859.6833</v>
       </c>
       <c r="AD8" t="n">
         <v>8</v>
       </c>
       <c r="AE8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AF8" t="n">
         <v>11</v>
       </c>
       <c r="AG8" t="n">
-        <v>7.3911</v>
+        <v>7.3807</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0.175</v>
       </c>
     </row>
     <row r="9">
@@ -3171,22 +3341,22 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M9" t="n">
-        <v>482</v>
+        <v>459</v>
       </c>
       <c r="N9" t="n">
-        <v>906</v>
+        <v>882</v>
       </c>
       <c r="O9" t="n">
-        <v>966.0092</v>
+        <v>919.796</v>
       </c>
       <c r="P9" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="Q9" t="n">
-        <v>20.5534</v>
+        <v>20.9045</v>
       </c>
       <c r="R9" t="n">
         <v>359.1909</v>
@@ -3204,28 +3374,28 @@
         <v>0.9025</v>
       </c>
       <c r="W9" t="n">
-        <v>0.03892433</v>
+        <v>0.03706695</v>
       </c>
       <c r="X9" t="n">
-        <v>0.03360409</v>
+        <v>0.03271392</v>
       </c>
       <c r="Y9" t="n">
-        <v>4.4545</v>
+        <v>4.7329</v>
       </c>
       <c r="Z9" t="n">
-        <v>453</v>
+        <v>415</v>
       </c>
       <c r="AA9" t="n">
-        <v>731</v>
+        <v>690</v>
       </c>
       <c r="AB9" t="n">
-        <v>543.4457</v>
+        <v>514.7178</v>
       </c>
       <c r="AC9" t="n">
-        <v>1016.1514</v>
+        <v>986.8377</v>
       </c>
       <c r="AD9" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AE9" t="n">
         <v>11</v>
@@ -3234,7 +3404,13 @@
         <v>10</v>
       </c>
       <c r="AG9" t="n">
-        <v>7.6519</v>
+        <v>7.5303</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0.0682</v>
       </c>
     </row>
     <row r="10">
@@ -3272,22 +3448,22 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M10" t="n">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="N10" t="n">
-        <v>981</v>
+        <v>992</v>
       </c>
       <c r="O10" t="n">
-        <v>2042.0723</v>
+        <v>2113.8713</v>
       </c>
       <c r="P10" t="n">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="Q10" t="n">
-        <v>21.7242</v>
+        <v>21.3522</v>
       </c>
       <c r="R10" t="n">
         <v>302.4508</v>
@@ -3305,37 +3481,43 @@
         <v>1</v>
       </c>
       <c r="W10" t="n">
-        <v>0.03711152</v>
+        <v>0.03765996</v>
       </c>
       <c r="X10" t="n">
-        <v>0.03959637</v>
+        <v>0.04004036</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.6451</v>
+        <v>1.9838</v>
       </c>
       <c r="Z10" t="n">
-        <v>314</v>
+        <v>357</v>
       </c>
       <c r="AA10" t="n">
-        <v>550</v>
+        <v>624</v>
       </c>
       <c r="AB10" t="n">
-        <v>456.7473</v>
+        <v>462.7473</v>
       </c>
       <c r="AC10" t="n">
-        <v>1098.9209</v>
+        <v>1109.9209</v>
       </c>
       <c r="AD10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AE10" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AF10" t="n">
         <v>12</v>
       </c>
       <c r="AG10" t="n">
-        <v>8.543200000000001</v>
+        <v>8.623699999999999</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>9</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0.3333</v>
       </c>
     </row>
     <row r="11">
@@ -3373,22 +3555,22 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M11" t="n">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="N11" t="n">
-        <v>1310</v>
+        <v>1313</v>
       </c>
       <c r="O11" t="n">
-        <v>4028.4167</v>
+        <v>3980.4461</v>
       </c>
       <c r="P11" t="n">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="Q11" t="n">
-        <v>24.8668</v>
+        <v>24.8778</v>
       </c>
       <c r="R11" t="n">
         <v>309.5219</v>
@@ -3406,25 +3588,25 @@
         <v>1</v>
       </c>
       <c r="W11" t="n">
-        <v>0.04516186</v>
+        <v>0.04533827</v>
       </c>
       <c r="X11" t="n">
-        <v>0.04631266</v>
+        <v>0.04641872</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.8462</v>
+        <v>5.1693</v>
       </c>
       <c r="Z11" t="n">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="AA11" t="n">
         <v>1290</v>
       </c>
       <c r="AB11" t="n">
-        <v>589.1442</v>
+        <v>590.3158</v>
       </c>
       <c r="AC11" t="n">
-        <v>1504.9819</v>
+        <v>1506.325</v>
       </c>
       <c r="AD11" t="n">
         <v>11</v>
@@ -3436,7 +3618,13 @@
         <v>16</v>
       </c>
       <c r="AG11" t="n">
-        <v>7.6136</v>
+        <v>7.62</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0.375</v>
       </c>
     </row>
     <row r="12">
@@ -3474,22 +3662,22 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="M12" t="n">
-        <v>815</v>
+        <v>870</v>
       </c>
       <c r="N12" t="n">
-        <v>1834</v>
+        <v>1902</v>
       </c>
       <c r="O12" t="n">
-        <v>4102.7476</v>
+        <v>4169.7598</v>
       </c>
       <c r="P12" t="n">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="Q12" t="n">
-        <v>18.6489</v>
+        <v>18.0509</v>
       </c>
       <c r="R12" t="n">
         <v>468.2742</v>
@@ -3507,28 +3695,28 @@
         <v>1</v>
       </c>
       <c r="W12" t="n">
-        <v>0.05304953</v>
+        <v>0.05662956</v>
       </c>
       <c r="X12" t="n">
-        <v>0.0537893</v>
+        <v>0.05578367</v>
       </c>
       <c r="Y12" t="n">
-        <v>4.271</v>
+        <v>5.1252</v>
       </c>
       <c r="Z12" t="n">
-        <v>715</v>
+        <v>801</v>
       </c>
       <c r="AA12" t="n">
-        <v>1723</v>
+        <v>1825</v>
       </c>
       <c r="AB12" t="n">
-        <v>930.6955</v>
+        <v>997.5656</v>
       </c>
       <c r="AC12" t="n">
-        <v>2072.2317</v>
+        <v>2153.1728</v>
       </c>
       <c r="AD12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AE12" t="n">
         <v>22</v>
@@ -3537,7 +3725,13 @@
         <v>25</v>
       </c>
       <c r="AG12" t="n">
-        <v>7.3385</v>
+        <v>7.3977</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0.4372</v>
       </c>
     </row>
     <row r="13">
@@ -3575,22 +3769,22 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M13" t="n">
-        <v>652</v>
+        <v>613</v>
       </c>
       <c r="N13" t="n">
-        <v>1393</v>
+        <v>1351</v>
       </c>
       <c r="O13" t="n">
-        <v>2361.1556</v>
+        <v>2381.1261</v>
       </c>
       <c r="P13" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="Q13" t="n">
-        <v>20.5318</v>
+        <v>20.8871</v>
       </c>
       <c r="R13" t="n">
         <v>422.9777</v>
@@ -3608,37 +3802,43 @@
         <v>1</v>
       </c>
       <c r="W13" t="n">
-        <v>0.04952526</v>
+        <v>0.04656286</v>
       </c>
       <c r="X13" t="n">
-        <v>0.04643179</v>
+        <v>0.04503183</v>
       </c>
       <c r="Y13" t="n">
-        <v>5.2012</v>
+        <v>5.4376</v>
       </c>
       <c r="Z13" t="n">
-        <v>610</v>
+        <v>561</v>
       </c>
       <c r="AA13" t="n">
-        <v>1227</v>
+        <v>1169</v>
       </c>
       <c r="AB13" t="n">
-        <v>732.2569</v>
+        <v>692.2569</v>
       </c>
       <c r="AC13" t="n">
-        <v>1573.7687</v>
+        <v>1529.3545</v>
       </c>
       <c r="AD13" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AE13" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AF13" t="n">
         <v>15</v>
       </c>
       <c r="AG13" t="n">
-        <v>7.0766</v>
+        <v>7.0375</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0.193</v>
       </c>
     </row>
     <row r="14">
@@ -3676,22 +3876,22 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="M14" t="n">
-        <v>636</v>
+        <v>608</v>
       </c>
       <c r="N14" t="n">
-        <v>1349</v>
+        <v>1318</v>
       </c>
       <c r="O14" t="n">
-        <v>2398.6825</v>
+        <v>2292.3982</v>
       </c>
       <c r="P14" t="n">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="Q14" t="n">
-        <v>18.8873</v>
+        <v>18.9454</v>
       </c>
       <c r="R14" t="n">
         <v>379.8478</v>
@@ -3709,28 +3909,28 @@
         <v>1</v>
       </c>
       <c r="W14" t="n">
-        <v>0.04783394</v>
+        <v>0.04572804</v>
       </c>
       <c r="X14" t="n">
-        <v>0.04201445</v>
+        <v>0.04104896</v>
       </c>
       <c r="Y14" t="n">
-        <v>6.0551</v>
+        <v>5.2653</v>
       </c>
       <c r="Z14" t="n">
-        <v>611</v>
+        <v>575</v>
       </c>
       <c r="AA14" t="n">
-        <v>1259</v>
+        <v>1220</v>
       </c>
       <c r="AB14" t="n">
-        <v>720.5706</v>
+        <v>688.6711</v>
       </c>
       <c r="AC14" t="n">
-        <v>1527.1829</v>
+        <v>1491.8692</v>
       </c>
       <c r="AD14" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AE14" t="n">
         <v>22</v>
@@ -3739,7 +3939,13 @@
         <v>19</v>
       </c>
       <c r="AG14" t="n">
-        <v>7.7579</v>
+        <v>7.7263</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>13</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0.4215</v>
       </c>
     </row>
     <row r="15">
@@ -3780,19 +3986,19 @@
         <v>10</v>
       </c>
       <c r="M15" t="n">
-        <v>300</v>
+        <v>317</v>
       </c>
       <c r="N15" t="n">
-        <v>702</v>
+        <v>719</v>
       </c>
       <c r="O15" t="n">
-        <v>2268.7657</v>
+        <v>2320.3221</v>
       </c>
       <c r="P15" t="n">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="Q15" t="n">
-        <v>26.6914</v>
+        <v>25.2209</v>
       </c>
       <c r="R15" t="n">
         <v>217.9239</v>
@@ -3810,28 +4016,28 @@
         <v>1</v>
       </c>
       <c r="W15" t="n">
-        <v>0.03397508</v>
+        <v>0.03590034</v>
       </c>
       <c r="X15" t="n">
-        <v>0.03054033</v>
+        <v>0.03127991</v>
       </c>
       <c r="Y15" t="n">
         <v>4.5888</v>
       </c>
       <c r="Z15" t="n">
-        <v>259</v>
+        <v>302</v>
       </c>
       <c r="AA15" t="n">
-        <v>579</v>
+        <v>622</v>
       </c>
       <c r="AB15" t="n">
-        <v>334.0366</v>
+        <v>355.5219</v>
       </c>
       <c r="AC15" t="n">
-        <v>789.2275</v>
+        <v>810.7128</v>
       </c>
       <c r="AD15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE15" t="n">
         <v>9</v>
@@ -3840,7 +4046,13 @@
         <v>9</v>
       </c>
       <c r="AG15" t="n">
-        <v>6.5975</v>
+        <v>6.9414</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>0.2283</v>
       </c>
     </row>
     <row r="16">
@@ -3881,19 +4093,19 @@
         <v>8</v>
       </c>
       <c r="M16" t="n">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="N16" t="n">
-        <v>904</v>
+        <v>910</v>
       </c>
       <c r="O16" t="n">
-        <v>2422.0256</v>
+        <v>2468.4104</v>
       </c>
       <c r="P16" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="Q16" t="n">
-        <v>26.3264</v>
+        <v>25.9833</v>
       </c>
       <c r="R16" t="n">
         <v>332.8944</v>
@@ -3911,28 +4123,28 @@
         <v>0.7919</v>
       </c>
       <c r="W16" t="n">
-        <v>0.03541171</v>
+        <v>0.03598287</v>
       </c>
       <c r="X16" t="n">
-        <v>0.03797362</v>
+        <v>0.03822566</v>
       </c>
       <c r="Y16" t="n">
         <v>2.4032</v>
       </c>
       <c r="Z16" t="n">
-        <v>310</v>
+        <v>351</v>
       </c>
       <c r="AA16" t="n">
-        <v>705</v>
+        <v>746</v>
       </c>
       <c r="AB16" t="n">
-        <v>418.6051</v>
+        <v>427.6762</v>
       </c>
       <c r="AC16" t="n">
-        <v>1017.394</v>
+        <v>1026.4651</v>
       </c>
       <c r="AD16" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AE16" t="n">
         <v>11</v>
@@ -3941,7 +4153,13 @@
         <v>16</v>
       </c>
       <c r="AG16" t="n">
-        <v>7.5598</v>
+        <v>7.6393</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>9</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>0.3895</v>
       </c>
     </row>
     <row r="17">
@@ -3979,22 +4197,22 @@
         <v>1</v>
       </c>
       <c r="L17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M17" t="n">
-        <v>154</v>
+        <v>192</v>
       </c>
       <c r="N17" t="n">
-        <v>505</v>
+        <v>542</v>
       </c>
       <c r="O17" t="n">
-        <v>65.4558</v>
+        <v>200.1665</v>
       </c>
       <c r="P17" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="Q17" t="n">
-        <v>10.9093</v>
+        <v>22.2407</v>
       </c>
       <c r="R17" t="n">
         <v>205.7756</v>
@@ -4012,37 +4230,43 @@
         <v>0.714</v>
       </c>
       <c r="W17" t="n">
-        <v>0.02276086</v>
+        <v>0.02837718</v>
       </c>
       <c r="X17" t="n">
-        <v>0.03087363</v>
+        <v>0.03313566</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.9439</v>
+        <v>2.4298</v>
       </c>
       <c r="Z17" t="n">
-        <v>119</v>
+        <v>176</v>
       </c>
       <c r="AA17" t="n">
-        <v>119</v>
+        <v>205</v>
       </c>
       <c r="AB17" t="n">
-        <v>170.9533</v>
+        <v>217.2376</v>
       </c>
       <c r="AC17" t="n">
-        <v>558.5462</v>
+        <v>605.0732</v>
       </c>
       <c r="AD17" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AE17" t="n">
         <v>7</v>
       </c>
       <c r="AF17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG17" t="n">
-        <v>5.3984</v>
+        <v>6.5763</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -4059,22 +4283,22 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M18" t="n">
-        <v>582</v>
+        <v>638</v>
       </c>
       <c r="N18" t="n">
-        <v>1325</v>
+        <v>1378</v>
       </c>
       <c r="O18" t="n">
-        <v>1512.6804</v>
+        <v>1557.1951</v>
       </c>
       <c r="P18" t="n">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="Q18" t="n">
-        <v>21.9229</v>
+        <v>20.4894</v>
       </c>
       <c r="R18" t="n">
         <v>387.9483</v>
@@ -4092,28 +4316,28 @@
         <v>1</v>
       </c>
       <c r="W18" t="n">
-        <v>0.04464217</v>
+        <v>0.04893764</v>
       </c>
       <c r="X18" t="n">
-        <v>0.04257712</v>
+        <v>0.04428021</v>
       </c>
       <c r="Y18" t="n">
-        <v>4.1243</v>
+        <v>4.382</v>
       </c>
       <c r="Z18" t="n">
-        <v>503</v>
+        <v>583</v>
       </c>
       <c r="AA18" t="n">
-        <v>859</v>
+        <v>1002</v>
       </c>
       <c r="AB18" t="n">
-        <v>672.4701</v>
+        <v>730.4701</v>
       </c>
       <c r="AC18" t="n">
-        <v>1535.9058</v>
+        <v>1588.0063</v>
       </c>
       <c r="AD18" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AE18" t="n">
         <v>16</v>
@@ -4122,7 +4346,13 @@
         <v>18</v>
       </c>
       <c r="AG18" t="n">
-        <v>7.6131</v>
+        <v>7.9873</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>0.1842</v>
       </c>
     </row>
     <row r="19">
@@ -4142,19 +4372,19 @@
         <v>2</v>
       </c>
       <c r="M19" t="n">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="N19" t="n">
-        <v>197</v>
+        <v>223</v>
       </c>
       <c r="O19" t="n">
-        <v>399.1909</v>
+        <v>413.1909</v>
       </c>
       <c r="P19" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="Q19" t="n">
-        <v>22.1773</v>
+        <v>20.6595</v>
       </c>
       <c r="R19" t="n">
         <v>87.0061</v>
@@ -4172,25 +4402,25 @@
         <v>0.5282</v>
       </c>
       <c r="W19" t="n">
-        <v>0.02641509</v>
+        <v>0.02984563</v>
       </c>
       <c r="X19" t="n">
-        <v>0.02276667</v>
+        <v>0.02577141</v>
       </c>
       <c r="Y19" t="n">
         <v>2.2987</v>
       </c>
       <c r="Z19" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AA19" t="n">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="AB19" t="n">
-        <v>89.01220000000001</v>
+        <v>97.7696</v>
       </c>
       <c r="AC19" t="n">
-        <v>222.5097</v>
+        <v>249.3381</v>
       </c>
       <c r="AD19" t="n">
         <v>2</v>
@@ -4199,10 +4429,16 @@
         <v>3</v>
       </c>
       <c r="AF19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG19" t="n">
-        <v>8.425000000000001</v>
+        <v>8.322100000000001</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>0.2</v>
       </c>
     </row>
     <row r="20">
@@ -4219,22 +4455,22 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M20" t="n">
-        <v>154</v>
+        <v>168</v>
       </c>
       <c r="N20" t="n">
-        <v>236</v>
+        <v>250</v>
       </c>
       <c r="O20" t="n">
-        <v>209.9828</v>
+        <v>209.397</v>
       </c>
       <c r="P20" t="n">
         <v>14</v>
       </c>
       <c r="Q20" t="n">
-        <v>14.9988</v>
+        <v>14.9569</v>
       </c>
       <c r="R20" t="n">
         <v>56.8701</v>
@@ -4252,37 +4488,43 @@
         <v>1</v>
       </c>
       <c r="W20" t="n">
-        <v>0.04188197</v>
+        <v>0.04568942</v>
       </c>
       <c r="X20" t="n">
-        <v>0.03328162</v>
+        <v>0.03525596</v>
       </c>
       <c r="Y20" t="n">
-        <v>7.0336</v>
+        <v>8.792</v>
       </c>
       <c r="Z20" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="AA20" t="n">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="AB20" t="n">
-        <v>167.8112</v>
+        <v>183.7107</v>
       </c>
       <c r="AC20" t="n">
-        <v>258.1665</v>
+        <v>275.4802</v>
       </c>
       <c r="AD20" t="n">
         <v>2</v>
       </c>
       <c r="AE20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF20" t="n">
         <v>6</v>
       </c>
       <c r="AG20" t="n">
-        <v>7.5189</v>
+        <v>7.6535</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>0.2857</v>
       </c>
     </row>
   </sheetData>
